--- a/Прогноз 2026 — Маркет и ОФД (с лидами).xlsx
+++ b/Прогноз 2026 — Маркет и ОФД (с лидами).xlsx
@@ -30,7 +30,7 @@
     <numFmt numFmtId="164" formatCode="#,##0 ₽"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -60,9 +60,6 @@
     </font>
     <font>
       <b val="1"/>
-    </font>
-    <font>
-      <color rgb="002F9E44"/>
     </font>
     <font>
       <name val="Montserrat"/>
@@ -154,7 +151,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -167,7 +164,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -185,21 +181,21 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="13" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="13" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="12" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="12" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1722,10 +1718,10 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>74978132.02954279</v>
+        <v>119039603</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>18349014.61460987</v>
+        <v>37544672.43728799</v>
       </c>
     </row>
     <row r="7">
@@ -1735,7 +1731,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>61842622.0403484</v>
+        <v>49034607</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>15306086.82974042</v>
@@ -1748,10 +1744,10 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>58910724.97</v>
+        <v>44473700</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>18908534.4</v>
+        <v>18897934.4</v>
       </c>
     </row>
     <row r="9">
@@ -1761,10 +1757,10 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>0.9525909967330377</v>
+        <v>0.906985957897042</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>1.235360455636503</v>
+        <v>1.234667920691555</v>
       </c>
     </row>
     <row r="10">
@@ -1773,11 +1769,11 @@
           <t>YoY к 2025, %</t>
         </is>
       </c>
-      <c r="B10" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="10" t="n">
-        <v>0</v>
+      <c r="B10" s="9" t="n">
+        <v>-0.2083540165606678</v>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>-0.1571918488066785</v>
       </c>
     </row>
     <row r="11">
@@ -1787,10 +1783,10 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>58910724.97</v>
+        <v>93076114.69332391</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>18908534.4</v>
+        <v>38625598.4183249</v>
       </c>
     </row>
     <row r="12">
@@ -1800,10 +1796,10 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>93153136.83697945</v>
+        <v>101995713.5958934</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>29350174.13771413</v>
+        <v>43317847.53680471</v>
       </c>
     </row>
     <row r="13">
@@ -1813,10 +1809,10 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>146790641.0524629</v>
+        <v>108426695.0560018</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>45525328.90231529</v>
+        <v>46488369.60313693</v>
       </c>
     </row>
     <row r="14">
@@ -1826,10 +1822,10 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.7857054233731521</v>
+        <v>0.7818920119661682</v>
       </c>
       <c r="C14" s="9" t="n">
-        <v>1.030493178905892</v>
+        <v>1.028790395836917</v>
       </c>
     </row>
     <row r="15">
@@ -1838,11 +1834,11 @@
           <t>Выполнение плана — БАЗА, %</t>
         </is>
       </c>
-      <c r="B15" s="11" t="n">
-        <v>1.242404075901429</v>
-      </c>
-      <c r="C15" s="11" t="n">
-        <v>1.599550425685798</v>
+      <c r="B15" s="10" t="n">
+        <v>0.8568216881225098</v>
+      </c>
+      <c r="C15" s="10" t="n">
+        <v>1.153768157364</v>
       </c>
     </row>
     <row r="16">
@@ -1852,10 +1848,10 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>1.957779382855586</v>
+        <v>0.9108455700747073</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>2.481077586916688</v>
+        <v>1.238214814120109</v>
       </c>
     </row>
     <row r="17">
@@ -1866,7 +1862,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>план будет выполнен</t>
+          <t>недовыполнение</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -1905,11 +1901,11 @@
           <t>Годовой план</t>
         </is>
       </c>
-      <c r="B21" s="12" t="n">
-        <v>7729.591648355621</v>
-      </c>
-      <c r="C21" s="12" t="n">
-        <v>3606.283371241205</v>
+      <c r="B21" s="11" t="n">
+        <v>6399</v>
+      </c>
+      <c r="C21" s="11" t="n">
+        <v>7375.265327374596</v>
       </c>
     </row>
     <row r="22">
@@ -1918,10 +1914,10 @@
           <t>План YTD (янв–май)</t>
         </is>
       </c>
-      <c r="B22" s="12" t="n">
-        <v>6398.966448988807</v>
-      </c>
-      <c r="C22" s="12" t="n">
+      <c r="B22" s="11" t="n">
+        <v>2737</v>
+      </c>
+      <c r="C22" s="11" t="n">
         <v>3008.397945204254</v>
       </c>
     </row>
@@ -1931,11 +1927,11 @@
           <t>Факт YTD (янв–май)</t>
         </is>
       </c>
-      <c r="B23" s="13" t="n">
-        <v>5978</v>
-      </c>
-      <c r="C23" s="13" t="n">
-        <v>3189</v>
+      <c r="B23" s="12" t="n">
+        <v>2458</v>
+      </c>
+      <c r="C23" s="12" t="n">
+        <v>3187</v>
       </c>
     </row>
     <row r="24">
@@ -1945,10 +1941,10 @@
         </is>
       </c>
       <c r="B24" s="9" t="n">
-        <v>0.9342133683080445</v>
+        <v>0.8980635732553891</v>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1.060032634673098</v>
+        <v>1.05936782900695</v>
       </c>
     </row>
     <row r="25">
@@ -1957,11 +1953,11 @@
           <t>YoY к 2025, %</t>
         </is>
       </c>
-      <c r="B25" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="10" t="n">
-        <v>0</v>
+      <c r="B25" s="9" t="n">
+        <v>-0.3168426903835464</v>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>-0.2738664843928002</v>
       </c>
     </row>
     <row r="26">
@@ -1970,11 +1966,11 @@
           <t>Прогноз года — НИЗ</t>
         </is>
       </c>
-      <c r="B26" s="12" t="n">
-        <v>5978</v>
-      </c>
-      <c r="C26" s="12" t="n">
-        <v>3189</v>
+      <c r="B26" s="11" t="n">
+        <v>4749.035887506989</v>
+      </c>
+      <c r="C26" s="11" t="n">
+        <v>5959.11800642271</v>
       </c>
     </row>
     <row r="27">
@@ -1983,11 +1979,11 @@
           <t>Прогноз года — БАЗА</t>
         </is>
       </c>
-      <c r="B27" s="13" t="n">
-        <v>9326.191927586042</v>
-      </c>
-      <c r="C27" s="13" t="n">
-        <v>4978.265237470123</v>
+      <c r="B27" s="12" t="n">
+        <v>5370.971244904632</v>
+      </c>
+      <c r="C27" s="12" t="n">
+        <v>7082.243156846213</v>
       </c>
     </row>
     <row r="28">
@@ -1996,11 +1992,11 @@
           <t>Прогноз года — ВЕРХ</t>
         </is>
       </c>
-      <c r="B28" s="12" t="n">
-        <v>14509.28464364729</v>
-      </c>
-      <c r="C28" s="12" t="n">
-        <v>7750.225049538408</v>
+      <c r="B28" s="11" t="n">
+        <v>5801.397388070602</v>
+      </c>
+      <c r="C28" s="11" t="n">
+        <v>7813.118818211061</v>
       </c>
     </row>
     <row r="29">
@@ -2010,10 +2006,10 @@
         </is>
       </c>
       <c r="B29" s="9" t="n">
-        <v>0.7733914379903559</v>
+        <v>0.7421528188009048</v>
       </c>
       <c r="C29" s="9" t="n">
-        <v>0.8842899106129907</v>
+        <v>0.8079869322537312</v>
       </c>
     </row>
     <row r="30">
@@ -2022,11 +2018,11 @@
           <t>Выполнение плана — БАЗА, %</t>
         </is>
       </c>
-      <c r="B30" s="11" t="n">
-        <v>1.206556872842057</v>
-      </c>
-      <c r="C30" s="11" t="n">
-        <v>1.380442057651368</v>
+      <c r="B30" s="10" t="n">
+        <v>0.8393454047358389</v>
+      </c>
+      <c r="C30" s="10" t="n">
+        <v>0.9602696096314284</v>
       </c>
     </row>
     <row r="31">
@@ -2036,10 +2032,10 @@
         </is>
       </c>
       <c r="B31" s="9" t="n">
-        <v>1.877108818126759</v>
+        <v>0.9066099996984844</v>
       </c>
       <c r="C31" s="9" t="n">
-        <v>2.149089312099994</v>
+        <v>1.05936782900695</v>
       </c>
     </row>
     <row r="32">
@@ -2050,12 +2046,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>план будет выполнен</t>
+          <t>существенный недобор</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>план будет выполнен</t>
+          <t>на грани плана</t>
         </is>
       </c>
     </row>
@@ -2077,200 +2073,200 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="18" t="inlineStr">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>Методология прогноза 2026 — Маркет и ОФД</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="19" t="inlineStr"/>
+      <c r="A2" s="18" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="20" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
         <is>
           <t>1. ИСТОЧНИКИ ДАННЫХ</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="19" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>• Царь свод все разрезы.xlsx — помесячный план и факт по проектам.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">    Маркет = проекты п470 + п47101; ОФД = проект п453 (п45302 — техника/ФН/услуги внедрения — исключён).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="19" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>• data (15).xlsx — рекламный факт (целевые лиды по продукту): выручка и оплаты по месяцам.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>• Дашборды Контекст (PNG) — расход, оплаты, CPL по месяцам (распознано с экрана, суммы сверены с «Итого»).</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="19" t="inlineStr"/>
+      <c r="A8" s="18" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>2. ГОРИЗОНТ И ОБУЧАЮЩАЯ ВЫБОРКА</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>• Факт известен по Май 2026 включительно (YTD). Прогнозируются оставшиеся месяцы до декабря 2026.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>• Обучающий ряд: янв 2025 – последний завершённый месяц 2026 (~17 точек). Июнь 2026 неполный — в обучение не берётся.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="inlineStr"/>
+      <c r="A12" s="18" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>3. МОДЕЛИ (считаются независимо, затем ансамбль)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="19" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>• Plan-pacing: оставшийся месяц = план месяца × (факт YTD ÷ план YTD).</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="19" t="inlineStr">
+      <c r="A15" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">    Самый бизнес-обоснованный — план уже содержит сезонность, а текущий темп выполнения переносится на остаток.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="19" t="inlineStr">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>• Сезонный YoY: оставшийся месяц = факт того же месяца 2025 × (1 + g), g — прирост YTD-2026 к тому же периоду 2025.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="19" t="inlineStr">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>• ETS / Holt (statsmodels ExponentialSmoothing): аддитивный демпфированный тренд; сезонность period=12, если ≥24 точек.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="19" t="inlineStr">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>• Регрессия + сезонные дамми (scikit-learn LinearRegression): линейный тренд по времени + 11 месячных индикаторов.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="19" t="inlineStr"/>
+      <c r="A19" s="18" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>4. АНСАМБЛЬ И СЦЕНАРИИ</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="19" t="inlineStr">
+      <c r="A21" s="18" t="inlineStr">
         <is>
           <t>• База = взвешенное среднее доступных методов: plan-pacing 0.40, сезонный YoY 0.25, ETS 0.15, регрессия 0.20.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="19" t="inlineStr">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>• Коридор: НИЗ = минимум по методам в каждом месяце, ВЕРХ = максимум. Сумма за год даёт сценарии низ/база/верх.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="19" t="inlineStr">
+      <c r="A23" s="18" t="inlineStr">
         <is>
           <t>• Отрицательные прогнозы обнуляются.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="19" t="inlineStr"/>
+      <c r="A24" s="18" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="20" t="inlineStr">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>5. ВЫПОЛНЕНИЕ ПЛАНА</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="19" t="inlineStr">
+      <c r="A26" s="18" t="inlineStr">
         <is>
           <t>• Прогноз года = факт YTD + Σ прогноза остатка. Выполнение плана = прогноз года ÷ годовой план × 100%.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="19" t="inlineStr">
+      <c r="A27" s="18" t="inlineStr">
         <is>
           <t>• Вывод: ≥100% — план будет выполнен; 95–100% — на грани; 85–95% — недовыполнение; &lt;85% — существенный недобор.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="19" t="inlineStr"/>
+      <c r="A28" s="18" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="20" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>6. ОГРАНИЧЕНИЯ</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="19" t="inlineStr">
+      <c r="A30" s="18" t="inlineStr">
         <is>
           <t>• Короткий ряд (~1.5 года) — сезонные модели работают на пределе; ставка сделана на plan-pacing и YoY.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="19" t="inlineStr">
+      <c r="A31" s="18" t="inlineStr">
         <is>
           <t>• Рекламные расход/CPL сняты с дашбордов распознаванием — возможны мелкие неточности (итоги сверены).</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="19" t="inlineStr">
+      <c r="A32" s="18" t="inlineStr">
         <is>
           <t>• Прогноз не учитывает разовые акции, изменения цен и план-факт корректировки после даты выгрузки.</t>
         </is>
@@ -2405,41 +2401,41 @@
       <c r="C4" t="n">
         <v>2026</v>
       </c>
-      <c r="D4" s="21" t="n">
-        <v>11976465</v>
-      </c>
-      <c r="E4" s="21" t="n">
-        <v>11920770</v>
-      </c>
-      <c r="F4" s="21" t="n">
-        <v>13959080</v>
-      </c>
-      <c r="G4" s="21" t="n">
-        <v>13111598</v>
-      </c>
-      <c r="H4" s="21" t="n">
-        <v>10874709</v>
-      </c>
-      <c r="I4" s="21" t="n">
-        <v>13135510</v>
-      </c>
-      <c r="J4" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="21" t="n">
-        <v>0</v>
+      <c r="D4" s="20" t="n">
+        <v>9780158</v>
+      </c>
+      <c r="E4" s="20" t="n">
+        <v>9456800</v>
+      </c>
+      <c r="F4" s="20" t="n">
+        <v>10981834</v>
+      </c>
+      <c r="G4" s="20" t="n">
+        <v>10450826</v>
+      </c>
+      <c r="H4" s="20" t="n">
+        <v>8364989</v>
+      </c>
+      <c r="I4" s="20" t="n">
+        <v>10320988</v>
+      </c>
+      <c r="J4" s="20" t="n">
+        <v>10125275</v>
+      </c>
+      <c r="K4" s="20" t="n">
+        <v>9011271</v>
+      </c>
+      <c r="L4" s="20" t="n">
+        <v>8788064</v>
+      </c>
+      <c r="M4" s="20" t="n">
+        <v>9948492</v>
+      </c>
+      <c r="N4" s="20" t="n">
+        <v>9708061</v>
+      </c>
+      <c r="O4" s="20" t="n">
+        <v>12102845</v>
       </c>
     </row>
     <row r="5">
@@ -2456,41 +2452,41 @@
       <c r="C5" t="n">
         <v>2025</v>
       </c>
-      <c r="D5" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="21" t="n">
-        <v>0</v>
+      <c r="D5" s="20" t="n">
+        <v>10566339</v>
+      </c>
+      <c r="E5" s="20" t="n">
+        <v>10162594</v>
+      </c>
+      <c r="F5" s="20" t="n">
+        <v>11323288</v>
+      </c>
+      <c r="G5" s="20" t="n">
+        <v>14129486</v>
+      </c>
+      <c r="H5" s="20" t="n">
+        <v>9997066</v>
+      </c>
+      <c r="I5" s="20" t="n">
+        <v>11423141</v>
+      </c>
+      <c r="J5" s="20" t="n">
+        <v>9919931</v>
+      </c>
+      <c r="K5" s="20" t="n">
+        <v>7919160</v>
+      </c>
+      <c r="L5" s="20" t="n">
+        <v>9186864</v>
+      </c>
+      <c r="M5" s="20" t="n">
+        <v>8738891</v>
+      </c>
+      <c r="N5" s="20" t="n">
+        <v>7976369</v>
+      </c>
+      <c r="O5" s="20" t="n">
+        <v>11983893</v>
       </c>
     </row>
     <row r="6">
@@ -2507,40 +2503,40 @@
       <c r="C6" t="n">
         <v>2026</v>
       </c>
-      <c r="D6" s="21" t="n">
-        <v>11172387</v>
-      </c>
-      <c r="E6" s="21" t="n">
-        <v>13264451</v>
-      </c>
-      <c r="F6" s="21" t="n">
-        <v>13054626</v>
-      </c>
-      <c r="G6" s="21" t="n">
-        <v>11472181</v>
-      </c>
-      <c r="H6" s="21" t="n">
-        <v>9947080</v>
-      </c>
-      <c r="I6" s="21" t="n">
-        <v>3438100</v>
-      </c>
-      <c r="J6" s="21" t="n">
+      <c r="D6" s="20" t="n">
+        <v>8241025</v>
+      </c>
+      <c r="E6" s="20" t="n">
+        <v>9199025</v>
+      </c>
+      <c r="F6" s="20" t="n">
+        <v>10261583</v>
+      </c>
+      <c r="G6" s="20" t="n">
+        <v>8993089</v>
+      </c>
+      <c r="H6" s="20" t="n">
+        <v>7778978</v>
+      </c>
+      <c r="I6" s="20" t="n">
+        <v>3207489</v>
+      </c>
+      <c r="J6" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="K6" s="21" t="n">
+      <c r="K6" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="21" t="n">
+      <c r="L6" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="M6" s="21" t="n">
+      <c r="M6" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="N6" s="21" t="n">
+      <c r="N6" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="O6" s="21" t="n">
+      <c r="O6" s="20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2558,41 +2554,41 @@
       <c r="C7" t="n">
         <v>2026</v>
       </c>
-      <c r="D7" s="21" t="n">
+      <c r="D7" s="20" t="n">
         <v>2810130</v>
       </c>
-      <c r="E7" s="21" t="n">
+      <c r="E7" s="20" t="n">
         <v>3106809</v>
       </c>
-      <c r="F7" s="21" t="n">
+      <c r="F7" s="20" t="n">
         <v>3178600</v>
       </c>
-      <c r="G7" s="21" t="n">
+      <c r="G7" s="20" t="n">
         <v>3241747</v>
       </c>
-      <c r="H7" s="21" t="n">
+      <c r="H7" s="20" t="n">
         <v>2968801</v>
       </c>
-      <c r="I7" s="21" t="n">
+      <c r="I7" s="20" t="n">
         <v>3042928</v>
       </c>
-      <c r="J7" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="21" t="n">
-        <v>0</v>
+      <c r="J7" s="20" t="n">
+        <v>3031387</v>
+      </c>
+      <c r="K7" s="20" t="n">
+        <v>2992992</v>
+      </c>
+      <c r="L7" s="20" t="n">
+        <v>2901985</v>
+      </c>
+      <c r="M7" s="20" t="n">
+        <v>3277977</v>
+      </c>
+      <c r="N7" s="20" t="n">
+        <v>3197016</v>
+      </c>
+      <c r="O7" s="20" t="n">
+        <v>3794301</v>
       </c>
     </row>
     <row r="8">
@@ -2609,41 +2605,41 @@
       <c r="C8" t="n">
         <v>2025</v>
       </c>
-      <c r="D8" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="21" t="n">
-        <v>0</v>
+      <c r="D8" s="20" t="n">
+        <v>4247510</v>
+      </c>
+      <c r="E8" s="20" t="n">
+        <v>4139667</v>
+      </c>
+      <c r="F8" s="20" t="n">
+        <v>4230687</v>
+      </c>
+      <c r="G8" s="20" t="n">
+        <v>5801237</v>
+      </c>
+      <c r="H8" s="20" t="n">
+        <v>4003480</v>
+      </c>
+      <c r="I8" s="20" t="n">
+        <v>4119079</v>
+      </c>
+      <c r="J8" s="20" t="n">
+        <v>3662365</v>
+      </c>
+      <c r="K8" s="20" t="n">
+        <v>3036271</v>
+      </c>
+      <c r="L8" s="20" t="n">
+        <v>3091534</v>
+      </c>
+      <c r="M8" s="20" t="n">
+        <v>3457517</v>
+      </c>
+      <c r="N8" s="20" t="n">
+        <v>2915835</v>
+      </c>
+      <c r="O8" s="20" t="n">
+        <v>5425473</v>
       </c>
     </row>
     <row r="9">
@@ -2660,40 +2656,40 @@
       <c r="C9" t="n">
         <v>2026</v>
       </c>
-      <c r="D9" s="21" t="n">
+      <c r="D9" s="20" t="n">
         <v>4051268</v>
       </c>
-      <c r="E9" s="21" t="n">
+      <c r="E9" s="20" t="n">
         <v>4117291</v>
       </c>
-      <c r="F9" s="21" t="n">
+      <c r="F9" s="20" t="n">
         <v>4177257</v>
       </c>
-      <c r="G9" s="21" t="n">
+      <c r="G9" s="20" t="n">
         <v>3708388</v>
       </c>
-      <c r="H9" s="21" t="n">
-        <v>2854330</v>
-      </c>
-      <c r="I9" s="21" t="n">
-        <v>885212</v>
-      </c>
-      <c r="J9" s="21" t="n">
+      <c r="H9" s="20" t="n">
+        <v>2843730</v>
+      </c>
+      <c r="I9" s="20" t="n">
+        <v>1188408</v>
+      </c>
+      <c r="J9" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="K9" s="21" t="n">
+      <c r="K9" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="L9" s="21" t="n">
+      <c r="L9" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="M9" s="21" t="n">
+      <c r="M9" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="N9" s="21" t="n">
+      <c r="N9" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="O9" s="21" t="n">
+      <c r="O9" s="20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2730,7 +2726,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Проекты п470, п47101 · факт по Май, далее прогноз (база) и коридор низ/верх</t>
+          <t>Проекты Продукт = Маркет · Подключение · Онлайн (дашборд) · факт по Май, далее прогноз (база) и коридор низ/верх</t>
         </is>
       </c>
     </row>
@@ -2778,13 +2774,13 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>11976465.28439866</v>
+        <v>9780158</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>0</v>
+        <v>10566339</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>11172387.06</v>
+        <v>8241025</v>
       </c>
       <c r="E5" s="6" t="n"/>
       <c r="F5" s="6" t="n"/>
@@ -2797,13 +2793,13 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>11920770.22500039</v>
+        <v>9456800</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>0</v>
+        <v>10162594</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>13264451.47</v>
+        <v>9199025</v>
       </c>
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
@@ -2816,13 +2812,13 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>13959079.78723557</v>
+        <v>10981834</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0</v>
+        <v>11323288</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>13054626.16</v>
+        <v>10261583</v>
       </c>
       <c r="E7" s="6" t="n"/>
       <c r="F7" s="6" t="n"/>
@@ -2835,13 +2831,13 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>13111598.14672046</v>
+        <v>10450826</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>0</v>
+        <v>14129486</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>11472180.65</v>
+        <v>8993089</v>
       </c>
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="n"/>
@@ -2854,13 +2850,13 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>10874708.59699332</v>
+        <v>8364989</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>0</v>
+        <v>9997066</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>9947079.629999999</v>
+        <v>7778978</v>
       </c>
       <c r="E9" s="6" t="n"/>
       <c r="F9" s="6" t="n"/>
@@ -2873,20 +2869,20 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>13135509.98919439</v>
+        <v>10320988</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>0</v>
+        <v>11423141</v>
       </c>
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="6" t="n">
-        <v>8936488.821271282</v>
+        <v>9101776.480453128</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0</v>
+        <v>8534558.684505247</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>12512768.55320346</v>
+        <v>9360991.187623875</v>
       </c>
     </row>
     <row r="11">
@@ -2896,20 +2892,20 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>0</v>
+        <v>10125275</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>0</v>
+        <v>9919931</v>
       </c>
       <c r="D11" s="6" t="n"/>
       <c r="E11" s="6" t="n">
-        <v>4013857.399769391</v>
+        <v>8417917.967619848</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>0</v>
+        <v>7578916.400000003</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>11782144.99399984</v>
+        <v>9183482.244845971</v>
       </c>
     </row>
     <row r="12">
@@ -2919,20 +2915,20 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>0</v>
+        <v>9011271</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>0</v>
+        <v>7919160</v>
       </c>
       <c r="D12" s="6" t="n"/>
       <c r="E12" s="6" t="n">
-        <v>4095921.019549984</v>
+        <v>7203853.966861567</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0</v>
+        <v>5578145.400000005</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>11782144.99399982</v>
+        <v>8344623.875908504</v>
       </c>
     </row>
     <row r="13">
@@ -2942,20 +2938,20 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>0</v>
+        <v>8788064</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>0</v>
+        <v>9186864</v>
       </c>
       <c r="D13" s="6" t="n"/>
       <c r="E13" s="6" t="n">
-        <v>4177574.321231673</v>
+        <v>7614401.594095069</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>0</v>
+        <v>6845849.400000002</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>12140968.81621142</v>
+        <v>8258569.730360099</v>
       </c>
     </row>
     <row r="14">
@@ -2965,20 +2961,20 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>0</v>
+        <v>9948492</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>0</v>
+        <v>8738891</v>
       </c>
       <c r="D14" s="6" t="n"/>
       <c r="E14" s="6" t="n">
-        <v>4258819.356404955</v>
+        <v>7845053.186182311</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0</v>
+        <v>6397876.400000004</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>12682602.38403332</v>
+        <v>9023142.546251059</v>
       </c>
     </row>
     <row r="15">
@@ -2988,20 +2984,20 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>0</v>
+        <v>9708061</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>0</v>
+        <v>7976369</v>
       </c>
       <c r="D15" s="6" t="n"/>
       <c r="E15" s="6" t="n">
-        <v>4339658.166402371</v>
+        <v>7443083.243262713</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>0</v>
+        <v>5635354.400000005</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>13221527.78401611</v>
+        <v>8805075.005407915</v>
       </c>
     </row>
     <row r="16">
@@ -3011,43 +3007,43 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>0</v>
+        <v>12102845</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>0</v>
+        <v>11983893</v>
       </c>
       <c r="D16" s="6" t="n"/>
       <c r="E16" s="6" t="n">
-        <v>4420092.782349799</v>
+        <v>9895927.157418748</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0</v>
+        <v>8031714.008818635</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>13757758.55699898</v>
+        <v>10977110.46560442</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>ИТОГО год</t>
         </is>
       </c>
-      <c r="B17" s="15" t="n">
-        <v>74978132.02954279</v>
-      </c>
-      <c r="C17" s="14" t="n"/>
-      <c r="D17" s="15" t="n">
-        <v>58910724.97</v>
-      </c>
-      <c r="E17" s="15" t="n">
-        <v>93153136.83697945</v>
-      </c>
-      <c r="F17" s="15" t="n">
-        <v>58910724.97</v>
-      </c>
-      <c r="G17" s="15" t="n">
-        <v>146790641.0524629</v>
+      <c r="B17" s="14" t="n">
+        <v>119039603</v>
+      </c>
+      <c r="C17" s="13" t="n"/>
+      <c r="D17" s="14" t="n">
+        <v>44473700</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>101995713.5958934</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>93076114.69332391</v>
+      </c>
+      <c r="G17" s="14" t="n">
+        <v>108426695.0560018</v>
       </c>
     </row>
   </sheetData>
@@ -3084,7 +3080,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Проекты п470, п47101 · факт по Май, далее прогноз (база) и коридор низ/верх</t>
+          <t>Проекты Продукт = Маркет · Подключение · Онлайн (дашборд) · факт по Май, далее прогноз (база) и коридор низ/верх</t>
         </is>
       </c>
     </row>
@@ -3131,18 +3127,18 @@
           <t>Январь</t>
         </is>
       </c>
-      <c r="B5" s="12" t="n">
-        <v>1244.855181028614</v>
-      </c>
-      <c r="C5" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="12" t="n">
-        <v>1195</v>
-      </c>
-      <c r="E5" s="12" t="n"/>
-      <c r="F5" s="12" t="n"/>
-      <c r="G5" s="12" t="n"/>
+      <c r="B5" s="11" t="n">
+        <v>617</v>
+      </c>
+      <c r="C5" s="11" t="n">
+        <v>752</v>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>477</v>
+      </c>
+      <c r="E5" s="11" t="n"/>
+      <c r="F5" s="11" t="n"/>
+      <c r="G5" s="11" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -3150,18 +3146,18 @@
           <t>Февраль</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
-        <v>1236.363483450679</v>
-      </c>
-      <c r="C6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="12" t="n">
-        <v>1540</v>
-      </c>
-      <c r="E6" s="12" t="n"/>
-      <c r="F6" s="12" t="n"/>
-      <c r="G6" s="12" t="n"/>
+      <c r="B6" s="11" t="n">
+        <v>532</v>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>644</v>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>501</v>
+      </c>
+      <c r="E6" s="11" t="n"/>
+      <c r="F6" s="11" t="n"/>
+      <c r="G6" s="11" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -3169,18 +3165,18 @@
           <t>Март</t>
         </is>
       </c>
-      <c r="B7" s="12" t="n">
-        <v>1451.398885860066</v>
-      </c>
-      <c r="C7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="12" t="n">
-        <v>1268</v>
-      </c>
-      <c r="E7" s="12" t="n"/>
-      <c r="F7" s="12" t="n"/>
-      <c r="G7" s="12" t="n"/>
+      <c r="B7" s="11" t="n">
+        <v>600</v>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>706</v>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>600</v>
+      </c>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="11" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -3188,18 +3184,18 @@
           <t>Апрель</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n">
-        <v>1336.916599324724</v>
-      </c>
-      <c r="C8" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="12" t="n">
-        <v>1067</v>
-      </c>
-      <c r="E8" s="12" t="n"/>
-      <c r="F8" s="12" t="n"/>
-      <c r="G8" s="12" t="n"/>
+      <c r="B8" s="11" t="n">
+        <v>576</v>
+      </c>
+      <c r="C8" s="11" t="n">
+        <v>883</v>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>477</v>
+      </c>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="11" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -3207,18 +3203,18 @@
           <t>Май</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n">
-        <v>1129.432299324724</v>
-      </c>
-      <c r="C9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="12" t="n">
-        <v>908</v>
-      </c>
-      <c r="E9" s="12" t="n"/>
-      <c r="F9" s="12" t="n"/>
-      <c r="G9" s="12" t="n"/>
+      <c r="B9" s="11" t="n">
+        <v>412</v>
+      </c>
+      <c r="C9" s="11" t="n">
+        <v>613</v>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>403</v>
+      </c>
+      <c r="E9" s="11" t="n"/>
+      <c r="F9" s="11" t="n"/>
+      <c r="G9" s="11" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -3226,21 +3222,21 @@
           <t>Июнь</t>
         </is>
       </c>
-      <c r="B10" s="12" t="n">
-        <v>1330.625199366814</v>
-      </c>
-      <c r="C10" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="12" t="n"/>
-      <c r="E10" s="12" t="n">
-        <v>880.6252238868395</v>
-      </c>
-      <c r="F10" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="12" t="n">
-        <v>1243.087849456035</v>
+      <c r="B10" s="11" t="n">
+        <v>526</v>
+      </c>
+      <c r="C10" s="11" t="n">
+        <v>700</v>
+      </c>
+      <c r="D10" s="11" t="n"/>
+      <c r="E10" s="11" t="n">
+        <v>472.1624872282246</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>461.7158815494085</v>
+      </c>
+      <c r="G10" s="11" t="n">
+        <v>478.2101167315175</v>
       </c>
     </row>
     <row r="11">
@@ -3249,21 +3245,21 @@
           <t>Июль</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="12" t="n">
-        <v>391.4198173144633</v>
-      </c>
-      <c r="F11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="12" t="n">
-        <v>1195.599999999978</v>
+      <c r="B11" s="11" t="n">
+        <v>562</v>
+      </c>
+      <c r="C11" s="11" t="n">
+        <v>584</v>
+      </c>
+      <c r="D11" s="11" t="n"/>
+      <c r="E11" s="11" t="n">
+        <v>440.9630121903972</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>356.0000000000001</v>
+      </c>
+      <c r="G11" s="11" t="n">
+        <v>504.7117281695287</v>
       </c>
     </row>
     <row r="12">
@@ -3272,21 +3268,21 @@
           <t>Август</t>
         </is>
       </c>
-      <c r="B12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="12" t="n"/>
-      <c r="E12" s="12" t="n">
-        <v>399.4094018584508</v>
-      </c>
-      <c r="F12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="12" t="n">
-        <v>1195.599999999976</v>
+      <c r="B12" s="11" t="n">
+        <v>458</v>
+      </c>
+      <c r="C12" s="11" t="n">
+        <v>458</v>
+      </c>
+      <c r="D12" s="11" t="n"/>
+      <c r="E12" s="11" t="n">
+        <v>355.8579974503227</v>
+      </c>
+      <c r="F12" s="11" t="n">
+        <v>230.0000000000003</v>
+      </c>
+      <c r="G12" s="11" t="n">
+        <v>447.4082591923428</v>
       </c>
     </row>
     <row r="13">
@@ -3295,21 +3291,21 @@
           <t>Сентябрь</t>
         </is>
       </c>
-      <c r="B13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="12" t="n">
-        <v>407.3590384797184</v>
-      </c>
-      <c r="F13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="12" t="n">
-        <v>1195.599999999974</v>
+      <c r="B13" s="11" t="n">
+        <v>477</v>
+      </c>
+      <c r="C13" s="11" t="n">
+        <v>517</v>
+      </c>
+      <c r="D13" s="11" t="n"/>
+      <c r="E13" s="11" t="n">
+        <v>383.6197751567994</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>288.9999999999999</v>
+      </c>
+      <c r="G13" s="11" t="n">
+        <v>441.14108741163</v>
       </c>
     </row>
     <row r="14">
@@ -3318,21 +3314,21 @@
           <t>Октябрь</t>
         </is>
       </c>
-      <c r="B14" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="12" t="n"/>
-      <c r="E14" s="12" t="n">
-        <v>415.2689269178796</v>
-      </c>
-      <c r="F14" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="12" t="n">
-        <v>1195.599999999972</v>
+      <c r="B14" s="11" t="n">
+        <v>559</v>
+      </c>
+      <c r="C14" s="11" t="n">
+        <v>529</v>
+      </c>
+      <c r="D14" s="11" t="n"/>
+      <c r="E14" s="11" t="n">
+        <v>416.6644812727669</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>301.0000000000001</v>
+      </c>
+      <c r="G14" s="11" t="n">
+        <v>502.0175374497625</v>
       </c>
     </row>
     <row r="15">
@@ -3341,21 +3337,21 @@
           <t>Ноябрь</t>
         </is>
       </c>
-      <c r="B15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="12" t="n">
-        <v>423.13926591385</v>
-      </c>
-      <c r="F15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="12" t="n">
-        <v>1226.795106092374</v>
+      <c r="B15" s="11" t="n">
+        <v>489</v>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>456</v>
+      </c>
+      <c r="D15" s="11" t="n"/>
+      <c r="E15" s="11" t="n">
+        <v>363.6620446519421</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>228.0000000000002</v>
+      </c>
+      <c r="G15" s="11" t="n">
+        <v>439.1530873218853</v>
       </c>
     </row>
     <row r="16">
@@ -3364,44 +3360,44 @@
           <t>Декабрь</t>
         </is>
       </c>
-      <c r="B16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="12" t="n"/>
-      <c r="E16" s="12" t="n">
-        <v>430.9702532148405</v>
-      </c>
-      <c r="F16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="12" t="n">
-        <v>1279.001688098981</v>
+      <c r="B16" s="11" t="n">
+        <v>591</v>
+      </c>
+      <c r="C16" s="11" t="n">
+        <v>673</v>
+      </c>
+      <c r="D16" s="11" t="n"/>
+      <c r="E16" s="11" t="n">
+        <v>480.0414469541792</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>425.3200059575791</v>
+      </c>
+      <c r="G16" s="11" t="n">
+        <v>530.7555717939349</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>ИТОГО год</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
-        <v>7729.591648355621</v>
-      </c>
-      <c r="C17" s="14" t="n"/>
-      <c r="D17" s="16" t="n">
-        <v>5978</v>
-      </c>
-      <c r="E17" s="16" t="n">
-        <v>9326.191927586042</v>
-      </c>
-      <c r="F17" s="16" t="n">
-        <v>5978</v>
-      </c>
-      <c r="G17" s="16" t="n">
-        <v>14509.28464364729</v>
+      <c r="B17" s="15" t="n">
+        <v>6399</v>
+      </c>
+      <c r="C17" s="13" t="n"/>
+      <c r="D17" s="15" t="n">
+        <v>2458</v>
+      </c>
+      <c r="E17" s="15" t="n">
+        <v>5370.971244904632</v>
+      </c>
+      <c r="F17" s="15" t="n">
+        <v>4749.035887506989</v>
+      </c>
+      <c r="G17" s="15" t="n">
+        <v>5801.397388070602</v>
       </c>
     </row>
   </sheetData>
@@ -3427,341 +3423,341 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>Маркет — лиды 2026, помесячно (прогноз)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="23" t="inlineStr">
-        <is>
-          <t>Источник: ГЭП-анализ · CR2 лид→оплата = 36% · проекты п470, п47101</t>
+      <c r="A2" s="22" t="inlineStr">
+        <is>
+          <t>Источник: ГЭП-анализ · CR2 лид→оплата = 36%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>Годовой прогноз</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t>Лиды прогноз</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>Нужно лидов для плана</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="24" t="inlineStr">
         <is>
           <t>Выполнение по лидам</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="24" t="inlineStr">
         <is>
           <t>Оплаты прогноз</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="24" t="inlineStr">
         <is>
           <t>CR2</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="n">
+      <c r="A6" s="25" t="n">
         <v>20471</v>
       </c>
-      <c r="B6" s="26" t="n">
+      <c r="B6" s="25" t="n">
         <v>23758</v>
       </c>
-      <c r="C6" s="27" t="n">
+      <c r="C6" s="26" t="n">
         <v>0.8616466032494318</v>
       </c>
-      <c r="D6" s="26" t="n">
+      <c r="D6" s="25" t="n">
         <v>7310</v>
       </c>
-      <c r="E6" s="27" t="n">
+      <c r="E6" s="26" t="n">
         <v>0.36</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="28" t="inlineStr">
+      <c r="A8" s="27" t="inlineStr">
         <is>
           <t>Месяц</t>
         </is>
       </c>
-      <c r="B8" s="28" t="inlineStr">
+      <c r="B8" s="27" t="inlineStr">
         <is>
           <t>Лиды (прогноз)</t>
         </is>
       </c>
-      <c r="C8" s="28" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t>Нужно лидов для плана</t>
         </is>
       </c>
-      <c r="D8" s="28" t="inlineStr">
+      <c r="D8" s="27" t="inlineStr">
         <is>
           <t>Оплаты (прогноз)</t>
         </is>
       </c>
-      <c r="E8" s="28" t="inlineStr">
+      <c r="E8" s="27" t="inlineStr">
         <is>
           <t>CR2</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" s="28" t="inlineStr">
         <is>
           <t>Январь</t>
         </is>
       </c>
-      <c r="B9" s="30" t="n">
+      <c r="B9" s="29" t="n">
         <v>1647</v>
       </c>
-      <c r="C9" s="30" t="n">
+      <c r="C9" s="29" t="n">
         <v>1812</v>
       </c>
-      <c r="D9" s="30" t="n">
+      <c r="D9" s="29" t="n">
         <v>573</v>
       </c>
-      <c r="E9" s="31" t="n">
+      <c r="E9" s="30" t="n">
         <v>0.36</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>Февраль</t>
         </is>
       </c>
-      <c r="B10" s="30" t="n">
+      <c r="B10" s="29" t="n">
         <v>1736</v>
       </c>
-      <c r="C10" s="30" t="n">
+      <c r="C10" s="29" t="n">
         <v>1910</v>
       </c>
-      <c r="D10" s="30" t="n">
+      <c r="D10" s="29" t="n">
         <v>605</v>
       </c>
-      <c r="E10" s="31" t="n">
+      <c r="E10" s="30" t="n">
         <v>0.36</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="29" t="inlineStr">
+      <c r="A11" s="28" t="inlineStr">
         <is>
           <t>Март</t>
         </is>
       </c>
-      <c r="B11" s="30" t="n">
+      <c r="B11" s="29" t="n">
         <v>1881</v>
       </c>
-      <c r="C11" s="30" t="n">
+      <c r="C11" s="29" t="n">
         <v>2069</v>
       </c>
-      <c r="D11" s="30" t="n">
+      <c r="D11" s="29" t="n">
         <v>657</v>
       </c>
-      <c r="E11" s="31" t="n">
+      <c r="E11" s="30" t="n">
         <v>0.36</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="29" t="inlineStr">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>Апрель</t>
         </is>
       </c>
-      <c r="B12" s="30" t="n">
+      <c r="B12" s="29" t="n">
         <v>1822</v>
       </c>
-      <c r="C12" s="30" t="n">
+      <c r="C12" s="29" t="n">
         <v>2004</v>
       </c>
-      <c r="D12" s="30" t="n">
+      <c r="D12" s="29" t="n">
         <v>656</v>
       </c>
-      <c r="E12" s="31" t="n">
+      <c r="E12" s="30" t="n">
         <v>0.36</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="29" t="inlineStr">
+      <c r="A13" s="28" t="inlineStr">
         <is>
           <t>Май</t>
         </is>
       </c>
-      <c r="B13" s="30" t="n">
+      <c r="B13" s="29" t="n">
         <v>1772</v>
       </c>
-      <c r="C13" s="30" t="n">
+      <c r="C13" s="29" t="n">
         <v>2215</v>
       </c>
-      <c r="D13" s="30" t="n">
+      <c r="D13" s="29" t="n">
         <v>638</v>
       </c>
-      <c r="E13" s="31" t="n">
+      <c r="E13" s="30" t="n">
         <v>0.36</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="29" t="inlineStr">
+      <c r="A14" s="28" t="inlineStr">
         <is>
           <t>Июнь</t>
         </is>
       </c>
-      <c r="B14" s="30" t="n">
+      <c r="B14" s="29" t="n">
         <v>1594</v>
       </c>
-      <c r="C14" s="30" t="n">
+      <c r="C14" s="29" t="n">
         <v>1993</v>
       </c>
-      <c r="D14" s="30" t="n">
+      <c r="D14" s="29" t="n">
         <v>574</v>
       </c>
-      <c r="E14" s="31" t="n">
+      <c r="E14" s="30" t="n">
         <v>0.36</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="29" t="inlineStr">
+      <c r="A15" s="28" t="inlineStr">
         <is>
           <t>Июль</t>
         </is>
       </c>
-      <c r="B15" s="30" t="n">
+      <c r="B15" s="29" t="n">
         <v>1611</v>
       </c>
-      <c r="C15" s="30" t="n">
+      <c r="C15" s="29" t="n">
         <v>2014</v>
       </c>
-      <c r="D15" s="30" t="n">
+      <c r="D15" s="29" t="n">
         <v>580</v>
       </c>
-      <c r="E15" s="31" t="n">
+      <c r="E15" s="30" t="n">
         <v>0.36</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="29" t="inlineStr">
+      <c r="A16" s="28" t="inlineStr">
         <is>
           <t>Август</t>
         </is>
       </c>
-      <c r="B16" s="30" t="n">
+      <c r="B16" s="29" t="n">
         <v>1631</v>
       </c>
-      <c r="C16" s="30" t="n">
+      <c r="C16" s="29" t="n">
         <v>1794</v>
       </c>
-      <c r="D16" s="30" t="n">
+      <c r="D16" s="29" t="n">
         <v>587</v>
       </c>
-      <c r="E16" s="31" t="n">
+      <c r="E16" s="30" t="n">
         <v>0.36</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="29" t="inlineStr">
+      <c r="A17" s="28" t="inlineStr">
         <is>
           <t>Сентябрь</t>
         </is>
       </c>
-      <c r="B17" s="30" t="n">
+      <c r="B17" s="29" t="n">
         <v>1586</v>
       </c>
-      <c r="C17" s="30" t="n">
+      <c r="C17" s="29" t="n">
         <v>1745</v>
       </c>
-      <c r="D17" s="30" t="n">
+      <c r="D17" s="29" t="n">
         <v>571</v>
       </c>
-      <c r="E17" s="31" t="n">
+      <c r="E17" s="30" t="n">
         <v>0.36</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="29" t="inlineStr">
+      <c r="A18" s="28" t="inlineStr">
         <is>
           <t>Октябрь</t>
         </is>
       </c>
-      <c r="B18" s="30" t="n">
+      <c r="B18" s="29" t="n">
         <v>1719</v>
       </c>
-      <c r="C18" s="30" t="n">
+      <c r="C18" s="29" t="n">
         <v>1891</v>
       </c>
-      <c r="D18" s="30" t="n">
+      <c r="D18" s="29" t="n">
         <v>619</v>
       </c>
-      <c r="E18" s="31" t="n">
+      <c r="E18" s="30" t="n">
         <v>0.36</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="29" t="inlineStr">
+      <c r="A19" s="28" t="inlineStr">
         <is>
           <t>Ноябрь</t>
         </is>
       </c>
-      <c r="B19" s="30" t="n">
+      <c r="B19" s="29" t="n">
         <v>1836</v>
       </c>
-      <c r="C19" s="30" t="n">
+      <c r="C19" s="29" t="n">
         <v>2020</v>
       </c>
-      <c r="D19" s="30" t="n">
+      <c r="D19" s="29" t="n">
         <v>661</v>
       </c>
-      <c r="E19" s="31" t="n">
+      <c r="E19" s="30" t="n">
         <v>0.36</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="29" t="inlineStr">
+      <c r="A20" s="28" t="inlineStr">
         <is>
           <t>Декабрь</t>
         </is>
       </c>
-      <c r="B20" s="30" t="n">
+      <c r="B20" s="29" t="n">
         <v>1636</v>
       </c>
-      <c r="C20" s="30" t="n">
+      <c r="C20" s="29" t="n">
         <v>2291</v>
       </c>
-      <c r="D20" s="30" t="n">
+      <c r="D20" s="29" t="n">
         <v>589</v>
       </c>
-      <c r="E20" s="31" t="n">
+      <c r="E20" s="30" t="n">
         <v>0.36</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="32" t="inlineStr">
+      <c r="A21" s="31" t="inlineStr">
         <is>
           <t>Итого 2026</t>
         </is>
       </c>
-      <c r="B21" s="33" t="n">
+      <c r="B21" s="32" t="n">
         <v>20471</v>
       </c>
-      <c r="C21" s="33" t="n">
+      <c r="C21" s="32" t="n">
         <v>23758</v>
       </c>
-      <c r="D21" s="33" t="n">
+      <c r="D21" s="32" t="n">
         <v>7310</v>
       </c>
-      <c r="E21" s="34" t="n">
+      <c r="E21" s="33" t="n">
         <v>0.36</v>
       </c>
     </row>
@@ -3798,7 +3794,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Проекты п453 · факт по Май, далее прогноз (база) и коридор низ/верх</t>
+          <t>Проекты Проект п453 · Подключение · Онлайн · факт по Май, далее прогноз (база) и коридор низ/верх</t>
         </is>
       </c>
     </row>
@@ -3849,7 +3845,7 @@
         <v>2810129.792756177</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>0</v>
+        <v>4247510.21</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>4051268</v>
@@ -3868,7 +3864,7 @@
         <v>3106809.006335288</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>0</v>
+        <v>4139667.24</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>4117291.34</v>
@@ -3887,7 +3883,7 @@
         <v>3178600.318375708</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0</v>
+        <v>4230686.78</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>4177257.07</v>
@@ -3906,7 +3902,7 @@
         <v>3241746.667406957</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>0</v>
+        <v>5801236.93</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>3708388.14</v>
@@ -3925,10 +3921,10 @@
         <v>2968801.044866289</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>0</v>
+        <v>4003480.27</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>2854329.85</v>
+        <v>2843729.85</v>
       </c>
       <c r="E9" s="6" t="n"/>
       <c r="F9" s="6" t="n"/>
@@ -3944,17 +3940,17 @@
         <v>3042927.784869445</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>0</v>
+        <v>4119078.85</v>
       </c>
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="6" t="n">
-        <v>2711459.079029309</v>
+        <v>3607218.915260342</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0</v>
+        <v>3414149.443999988</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>3781706.879999951</v>
+        <v>3757005.320959318</v>
       </c>
     </row>
     <row r="11">
@@ -3964,20 +3960,20 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>0</v>
+        <v>3031387.357925069</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>0</v>
+        <v>3662365.2</v>
       </c>
       <c r="D11" s="6" t="n"/>
       <c r="E11" s="6" t="n">
-        <v>1231020.56266535</v>
+        <v>3413275.795122174</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>0</v>
+        <v>2957435.793999986</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>3781706.879999946</v>
+        <v>3742756.726020012</v>
       </c>
     </row>
     <row r="12">
@@ -3987,20 +3983,20 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>0</v>
+        <v>2992991.751534346</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>0</v>
+        <v>3036270.56</v>
       </c>
       <c r="D12" s="6" t="n"/>
       <c r="E12" s="6" t="n">
-        <v>1254111.075487757</v>
+        <v>3136636.550911444</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0</v>
+        <v>2331341.153999985</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>3781706.87999994</v>
+        <v>3695350.902513886</v>
       </c>
     </row>
     <row r="13">
@@ -4010,20 +4006,20 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>0</v>
+        <v>2901984.613445907</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>0</v>
+        <v>3091534.05</v>
       </c>
       <c r="D13" s="6" t="n"/>
       <c r="E13" s="6" t="n">
-        <v>1277086.135746052</v>
+        <v>3113955.313009272</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>0</v>
+        <v>2386604.643999983</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>3781706.879999936</v>
+        <v>3680312.910176613</v>
       </c>
     </row>
     <row r="14">
@@ -4033,20 +4029,20 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>0</v>
+        <v>3277976.709883101</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>0</v>
+        <v>3457517.25</v>
       </c>
       <c r="D14" s="6" t="n"/>
       <c r="E14" s="6" t="n">
-        <v>1299946.320703056</v>
+        <v>3449607.984927707</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0</v>
+        <v>2752587.843999983</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>3781706.879999931</v>
+        <v>4047212.688466714</v>
       </c>
     </row>
     <row r="15">
@@ -4056,20 +4052,20 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>0</v>
+        <v>3197016.051724652</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>0</v>
+        <v>2915834.57</v>
       </c>
       <c r="D15" s="6" t="n"/>
       <c r="E15" s="6" t="n">
-        <v>1322692.204735274</v>
+        <v>3186874.829107625</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>0</v>
+        <v>2210905.163999981</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>3781706.879999925</v>
+        <v>3947253.161000401</v>
       </c>
     </row>
     <row r="16">
@@ -4079,43 +4075,43 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>0</v>
+        <v>3794301.338165053</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>0</v>
+        <v>5425472.9</v>
       </c>
       <c r="D16" s="6" t="n"/>
       <c r="E16" s="6" t="n">
-        <v>1345324.359347332</v>
+        <v>4512343.748466134</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0</v>
+        <v>3674639.974324989</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>3926553.222315652</v>
+        <v>4720543.493999979</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>ИТОГО год</t>
         </is>
       </c>
-      <c r="B17" s="15" t="n">
-        <v>18349014.61460987</v>
-      </c>
-      <c r="C17" s="14" t="n"/>
-      <c r="D17" s="15" t="n">
-        <v>18908534.4</v>
-      </c>
-      <c r="E17" s="15" t="n">
-        <v>29350174.13771413</v>
-      </c>
-      <c r="F17" s="15" t="n">
-        <v>18908534.4</v>
-      </c>
-      <c r="G17" s="15" t="n">
-        <v>45525328.90231529</v>
+      <c r="B17" s="14" t="n">
+        <v>37544672.43728799</v>
+      </c>
+      <c r="C17" s="13" t="n"/>
+      <c r="D17" s="14" t="n">
+        <v>18897934.4</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>43317847.53680471</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>38625598.4183249</v>
+      </c>
+      <c r="G17" s="14" t="n">
+        <v>46488369.60313693</v>
       </c>
     </row>
   </sheetData>
@@ -4152,7 +4148,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Проекты п453 · факт по Май, далее прогноз (база) и коридор низ/верх</t>
+          <t>Проекты Проект п453 · Подключение · Онлайн · факт по Май, далее прогноз (база) и коридор низ/верх</t>
         </is>
       </c>
     </row>
@@ -4199,18 +4195,18 @@
           <t>Январь</t>
         </is>
       </c>
-      <c r="B5" s="12" t="n">
+      <c r="B5" s="11" t="n">
         <v>553.1295998444964</v>
       </c>
-      <c r="C5" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="12" t="n">
+      <c r="C5" s="11" t="n">
+        <v>925</v>
+      </c>
+      <c r="D5" s="11" t="n">
         <v>712</v>
       </c>
-      <c r="E5" s="12" t="n"/>
-      <c r="F5" s="12" t="n"/>
-      <c r="G5" s="12" t="n"/>
+      <c r="E5" s="11" t="n"/>
+      <c r="F5" s="11" t="n"/>
+      <c r="G5" s="11" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -4218,18 +4214,18 @@
           <t>Февраль</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="11" t="n">
         <v>611.4680998825025</v>
       </c>
-      <c r="C6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="12" t="n">
+      <c r="C6" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="D6" s="11" t="n">
         <v>699</v>
       </c>
-      <c r="E6" s="12" t="n"/>
-      <c r="F6" s="12" t="n"/>
-      <c r="G6" s="12" t="n"/>
+      <c r="E6" s="11" t="n"/>
+      <c r="F6" s="11" t="n"/>
+      <c r="G6" s="11" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -4237,18 +4233,18 @@
           <t>Март</t>
         </is>
       </c>
-      <c r="B7" s="12" t="n">
+      <c r="B7" s="11" t="n">
         <v>621.6022998825026</v>
       </c>
-      <c r="C7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="12" t="n">
+      <c r="C7" s="11" t="n">
+        <v>785</v>
+      </c>
+      <c r="D7" s="11" t="n">
         <v>711</v>
       </c>
-      <c r="E7" s="12" t="n"/>
-      <c r="F7" s="12" t="n"/>
-      <c r="G7" s="12" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="11" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -4256,18 +4252,18 @@
           <t>Апрель</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="11" t="n">
         <v>637.577022890739</v>
       </c>
-      <c r="C8" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="12" t="n">
+      <c r="C8" s="11" t="n">
+        <v>1013</v>
+      </c>
+      <c r="D8" s="11" t="n">
         <v>576</v>
       </c>
-      <c r="E8" s="12" t="n"/>
-      <c r="F8" s="12" t="n"/>
-      <c r="G8" s="12" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="11" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -4275,18 +4271,18 @@
           <t>Май</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n">
+      <c r="B9" s="11" t="n">
         <v>584.6209227040131</v>
       </c>
-      <c r="C9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="12" t="n">
-        <v>491</v>
-      </c>
-      <c r="E9" s="12" t="n"/>
-      <c r="F9" s="12" t="n"/>
-      <c r="G9" s="12" t="n"/>
+      <c r="C9" s="11" t="n">
+        <v>866</v>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>489</v>
+      </c>
+      <c r="E9" s="11" t="n"/>
+      <c r="F9" s="11" t="n"/>
+      <c r="G9" s="11" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -4294,21 +4290,21 @@
           <t>Июнь</t>
         </is>
       </c>
-      <c r="B10" s="12" t="n">
+      <c r="B10" s="11" t="n">
         <v>597.8854260369515</v>
       </c>
-      <c r="C10" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="12" t="n"/>
-      <c r="E10" s="12" t="n">
-        <v>459.8375329743966</v>
-      </c>
-      <c r="F10" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="12" t="n">
-        <v>637.7999999999911</v>
+      <c r="C10" s="11" t="n">
+        <v>726</v>
+      </c>
+      <c r="D10" s="11" t="n"/>
+      <c r="E10" s="11" t="n">
+        <v>574.3371580430527</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>485.5999999999999</v>
+      </c>
+      <c r="G10" s="11" t="n">
+        <v>633.3805857756607</v>
       </c>
     </row>
     <row r="11">
@@ -4317,21 +4313,21 @@
           <t>Июль</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="12" t="n">
-        <v>210.7184337724339</v>
-      </c>
-      <c r="F11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="12" t="n">
-        <v>637.7999999999903</v>
+      <c r="B11" s="11" t="n">
+        <v>594.5740260369514</v>
+      </c>
+      <c r="C11" s="11" t="n">
+        <v>627</v>
+      </c>
+      <c r="D11" s="11" t="n"/>
+      <c r="E11" s="11" t="n">
+        <v>534.6838385656411</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>386.6</v>
+      </c>
+      <c r="G11" s="11" t="n">
+        <v>629.8725951466871</v>
       </c>
     </row>
     <row r="12">
@@ -4340,21 +4336,21 @@
           <t>Август</t>
         </is>
       </c>
-      <c r="B12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="12" t="n"/>
-      <c r="E12" s="12" t="n">
-        <v>215.0885992975308</v>
-      </c>
-      <c r="F12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="12" t="n">
-        <v>637.7999999999894</v>
+      <c r="B12" s="11" t="n">
+        <v>584.9120258783644</v>
+      </c>
+      <c r="C12" s="11" t="n">
+        <v>586</v>
+      </c>
+      <c r="D12" s="11" t="n"/>
+      <c r="E12" s="11" t="n">
+        <v>514.5393659549742</v>
+      </c>
+      <c r="F12" s="11" t="n">
+        <v>345.6000000000001</v>
+      </c>
+      <c r="G12" s="11" t="n">
+        <v>619.6369830148199</v>
       </c>
     </row>
     <row r="13">
@@ -4363,21 +4359,21 @@
           <t>Сентябрь</t>
         </is>
       </c>
-      <c r="B13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="12" t="n">
-        <v>219.4369139950022</v>
-      </c>
-      <c r="F13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="12" t="n">
-        <v>637.7999999999885</v>
+      <c r="B13" s="11" t="n">
+        <v>573.0697258783644</v>
+      </c>
+      <c r="C13" s="11" t="n">
+        <v>561</v>
+      </c>
+      <c r="D13" s="11" t="n"/>
+      <c r="E13" s="11" t="n">
+        <v>499.6359641188786</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>320.5999999999999</v>
+      </c>
+      <c r="G13" s="11" t="n">
+        <v>607.0916313733709</v>
       </c>
     </row>
     <row r="14">
@@ -4386,21 +4382,21 @@
           <t>Октябрь</t>
         </is>
       </c>
-      <c r="B14" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="12" t="n"/>
-      <c r="E14" s="12" t="n">
-        <v>223.7634871189863</v>
-      </c>
-      <c r="F14" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="12" t="n">
-        <v>641.3565807932582</v>
+      <c r="B14" s="11" t="n">
+        <v>641.4724260369514</v>
+      </c>
+      <c r="C14" s="11" t="n">
+        <v>603</v>
+      </c>
+      <c r="D14" s="11" t="n"/>
+      <c r="E14" s="11" t="n">
+        <v>544.3503545490897</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>362.6</v>
+      </c>
+      <c r="G14" s="11" t="n">
+        <v>679.5552513385867</v>
       </c>
     </row>
     <row r="15">
@@ -4409,21 +4405,21 @@
           <t>Ноябрь</t>
         </is>
       </c>
-      <c r="B15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="12" t="n">
-        <v>228.0684273773504</v>
-      </c>
-      <c r="F15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="12" t="n">
-        <v>670.0561825156869</v>
+      <c r="B15" s="11" t="n">
+        <v>628.7328258882317</v>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>511</v>
+      </c>
+      <c r="D15" s="11" t="n"/>
+      <c r="E15" s="11" t="n">
+        <v>503.5992871742177</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>270.6</v>
+      </c>
+      <c r="G15" s="11" t="n">
+        <v>666.0593287866208</v>
       </c>
     </row>
     <row r="16">
@@ -4432,44 +4428,44 @@
           <t>Декабрь</t>
         </is>
       </c>
-      <c r="B16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="12" t="n"/>
-      <c r="E16" s="12" t="n">
-        <v>232.3518429344227</v>
-      </c>
-      <c r="F16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="12" t="n">
-        <v>698.6122862295036</v>
+      <c r="B16" s="11" t="n">
+        <v>746.2209264145296</v>
+      </c>
+      <c r="C16" s="11" t="n">
+        <v>959</v>
+      </c>
+      <c r="D16" s="11" t="n"/>
+      <c r="E16" s="11" t="n">
+        <v>724.0971884403589</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>600.51800642271</v>
+      </c>
+      <c r="G16" s="11" t="n">
+        <v>790.5224427753153</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>ИТОГО год</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
-        <v>3606.283371241205</v>
-      </c>
-      <c r="C17" s="14" t="n"/>
-      <c r="D17" s="16" t="n">
-        <v>3189</v>
-      </c>
-      <c r="E17" s="16" t="n">
-        <v>4978.265237470123</v>
-      </c>
-      <c r="F17" s="16" t="n">
-        <v>3189</v>
-      </c>
-      <c r="G17" s="16" t="n">
-        <v>7750.225049538408</v>
+      <c r="B17" s="15" t="n">
+        <v>7375.265327374596</v>
+      </c>
+      <c r="C17" s="13" t="n"/>
+      <c r="D17" s="15" t="n">
+        <v>3187</v>
+      </c>
+      <c r="E17" s="15" t="n">
+        <v>7082.243156846213</v>
+      </c>
+      <c r="F17" s="15" t="n">
+        <v>5959.11800642271</v>
+      </c>
+      <c r="G17" s="15" t="n">
+        <v>7813.118818211061</v>
       </c>
     </row>
   </sheetData>
@@ -4495,341 +4491,341 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>ОФД — лиды 2026, помесячно (прогноз)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="23" t="inlineStr">
-        <is>
-          <t>Источник: ГЭП-анализ · CR2 лид→оплата = 46% · проект п453</t>
+      <c r="A2" s="22" t="inlineStr">
+        <is>
+          <t>Источник: ГЭП-анализ · CR2 лид→оплата = 46%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>Годовой прогноз</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t>Лиды прогноз</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>Минимум лидов для плана</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="24" t="inlineStr">
         <is>
           <t>Выполнение по лидам</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="24" t="inlineStr">
         <is>
           <t>Оплаты прогноз</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="24" t="inlineStr">
         <is>
           <t>CR2</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="n">
+      <c r="A6" s="25" t="n">
         <v>17196</v>
       </c>
-      <c r="B6" s="26" t="n">
+      <c r="B6" s="25" t="n">
         <v>14992</v>
       </c>
-      <c r="C6" s="27" t="n">
+      <c r="C6" s="26" t="n">
         <v>1.14701173959445</v>
       </c>
-      <c r="D6" s="26" t="n">
+      <c r="D6" s="25" t="n">
         <v>7938</v>
       </c>
-      <c r="E6" s="27" t="n">
+      <c r="E6" s="26" t="n">
         <v>0.46</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="28" t="inlineStr">
+      <c r="A8" s="27" t="inlineStr">
         <is>
           <t>Месяц</t>
         </is>
       </c>
-      <c r="B8" s="28" t="inlineStr">
+      <c r="B8" s="27" t="inlineStr">
         <is>
           <t>Лиды (прогноз)</t>
         </is>
       </c>
-      <c r="C8" s="28" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t>Минимум лидов для плана</t>
         </is>
       </c>
-      <c r="D8" s="28" t="inlineStr">
+      <c r="D8" s="27" t="inlineStr">
         <is>
           <t>Оплаты (прогноз)</t>
         </is>
       </c>
-      <c r="E8" s="28" t="inlineStr">
+      <c r="E8" s="27" t="inlineStr">
         <is>
           <t>CR2</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" s="28" t="inlineStr">
         <is>
           <t>Январь</t>
         </is>
       </c>
-      <c r="B9" s="30" t="n">
+      <c r="B9" s="29" t="n">
         <v>1326</v>
       </c>
-      <c r="C9" s="30" t="n">
+      <c r="C9" s="29" t="n">
         <v>1083</v>
       </c>
-      <c r="D9" s="30" t="n">
+      <c r="D9" s="29" t="n">
         <v>613</v>
       </c>
-      <c r="E9" s="31" t="n">
+      <c r="E9" s="30" t="n">
         <v>0.46</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>Февраль</t>
         </is>
       </c>
-      <c r="B10" s="30" t="n">
+      <c r="B10" s="29" t="n">
         <v>1439</v>
       </c>
-      <c r="C10" s="30" t="n">
+      <c r="C10" s="29" t="n">
         <v>1294</v>
       </c>
-      <c r="D10" s="30" t="n">
+      <c r="D10" s="29" t="n">
         <v>664</v>
       </c>
-      <c r="E10" s="31" t="n">
+      <c r="E10" s="30" t="n">
         <v>0.46</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="29" t="inlineStr">
+      <c r="A11" s="28" t="inlineStr">
         <is>
           <t>Март</t>
         </is>
       </c>
-      <c r="B11" s="30" t="n">
+      <c r="B11" s="29" t="n">
         <v>1460</v>
       </c>
-      <c r="C11" s="30" t="n">
+      <c r="C11" s="29" t="n">
         <v>1182</v>
       </c>
-      <c r="D11" s="30" t="n">
+      <c r="D11" s="29" t="n">
         <v>674</v>
       </c>
-      <c r="E11" s="31" t="n">
+      <c r="E11" s="30" t="n">
         <v>0.46</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="29" t="inlineStr">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>Апрель</t>
         </is>
       </c>
-      <c r="B12" s="30" t="n">
+      <c r="B12" s="29" t="n">
         <v>1393</v>
       </c>
-      <c r="C12" s="30" t="n">
+      <c r="C12" s="29" t="n">
         <v>1194</v>
       </c>
-      <c r="D12" s="30" t="n">
+      <c r="D12" s="29" t="n">
         <v>643</v>
       </c>
-      <c r="E12" s="31" t="n">
+      <c r="E12" s="30" t="n">
         <v>0.46</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="29" t="inlineStr">
+      <c r="A13" s="28" t="inlineStr">
         <is>
           <t>Май</t>
         </is>
       </c>
-      <c r="B13" s="30" t="n">
+      <c r="B13" s="29" t="n">
         <v>1452</v>
       </c>
-      <c r="C13" s="30" t="n">
+      <c r="C13" s="29" t="n">
         <v>1193</v>
       </c>
-      <c r="D13" s="30" t="n">
+      <c r="D13" s="29" t="n">
         <v>670</v>
       </c>
-      <c r="E13" s="31" t="n">
+      <c r="E13" s="30" t="n">
         <v>0.46</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="29" t="inlineStr">
+      <c r="A14" s="28" t="inlineStr">
         <is>
           <t>Июнь</t>
         </is>
       </c>
-      <c r="B14" s="30" t="n">
+      <c r="B14" s="29" t="n">
         <v>1345</v>
       </c>
-      <c r="C14" s="30" t="n">
+      <c r="C14" s="29" t="n">
         <v>1200</v>
       </c>
-      <c r="D14" s="30" t="n">
+      <c r="D14" s="29" t="n">
         <v>621</v>
       </c>
-      <c r="E14" s="31" t="n">
+      <c r="E14" s="30" t="n">
         <v>0.46</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="29" t="inlineStr">
+      <c r="A15" s="28" t="inlineStr">
         <is>
           <t>Июль</t>
         </is>
       </c>
-      <c r="B15" s="30" t="n">
+      <c r="B15" s="29" t="n">
         <v>1409</v>
       </c>
-      <c r="C15" s="30" t="n">
+      <c r="C15" s="29" t="n">
         <v>1213</v>
       </c>
-      <c r="D15" s="30" t="n">
+      <c r="D15" s="29" t="n">
         <v>650</v>
       </c>
-      <c r="E15" s="31" t="n">
+      <c r="E15" s="30" t="n">
         <v>0.46</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="29" t="inlineStr">
+      <c r="A16" s="28" t="inlineStr">
         <is>
           <t>Август</t>
         </is>
       </c>
-      <c r="B16" s="30" t="n">
+      <c r="B16" s="29" t="n">
         <v>1328</v>
       </c>
-      <c r="C16" s="30" t="n">
+      <c r="C16" s="29" t="n">
         <v>1220</v>
       </c>
-      <c r="D16" s="30" t="n">
+      <c r="D16" s="29" t="n">
         <v>613</v>
       </c>
-      <c r="E16" s="31" t="n">
+      <c r="E16" s="30" t="n">
         <v>0.46</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="29" t="inlineStr">
+      <c r="A17" s="28" t="inlineStr">
         <is>
           <t>Сентябрь</t>
         </is>
       </c>
-      <c r="B17" s="30" t="n">
+      <c r="B17" s="29" t="n">
         <v>1358</v>
       </c>
-      <c r="C17" s="30" t="n">
+      <c r="C17" s="29" t="n">
         <v>1228</v>
       </c>
-      <c r="D17" s="30" t="n">
+      <c r="D17" s="29" t="n">
         <v>627</v>
       </c>
-      <c r="E17" s="31" t="n">
+      <c r="E17" s="30" t="n">
         <v>0.46</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="29" t="inlineStr">
+      <c r="A18" s="28" t="inlineStr">
         <is>
           <t>Октябрь</t>
         </is>
       </c>
-      <c r="B18" s="30" t="n">
+      <c r="B18" s="29" t="n">
         <v>1625</v>
       </c>
-      <c r="C18" s="30" t="n">
+      <c r="C18" s="29" t="n">
         <v>1422</v>
       </c>
-      <c r="D18" s="30" t="n">
+      <c r="D18" s="29" t="n">
         <v>750</v>
       </c>
-      <c r="E18" s="31" t="n">
+      <c r="E18" s="30" t="n">
         <v>0.46</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="29" t="inlineStr">
+      <c r="A19" s="28" t="inlineStr">
         <is>
           <t>Ноябрь</t>
         </is>
       </c>
-      <c r="B19" s="30" t="n">
+      <c r="B19" s="29" t="n">
         <v>1517</v>
       </c>
-      <c r="C19" s="30" t="n">
+      <c r="C19" s="29" t="n">
         <v>1368</v>
       </c>
-      <c r="D19" s="30" t="n">
+      <c r="D19" s="29" t="n">
         <v>700</v>
       </c>
-      <c r="E19" s="31" t="n">
+      <c r="E19" s="30" t="n">
         <v>0.46</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="29" t="inlineStr">
+      <c r="A20" s="28" t="inlineStr">
         <is>
           <t>Декабрь</t>
         </is>
       </c>
-      <c r="B20" s="30" t="n">
+      <c r="B20" s="29" t="n">
         <v>1544</v>
       </c>
-      <c r="C20" s="30" t="n">
+      <c r="C20" s="29" t="n">
         <v>1395</v>
       </c>
-      <c r="D20" s="30" t="n">
+      <c r="D20" s="29" t="n">
         <v>713</v>
       </c>
-      <c r="E20" s="31" t="n">
+      <c r="E20" s="30" t="n">
         <v>0.46</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="32" t="inlineStr">
+      <c r="A21" s="31" t="inlineStr">
         <is>
           <t>Итого 2026</t>
         </is>
       </c>
-      <c r="B21" s="33" t="n">
+      <c r="B21" s="32" t="n">
         <v>17196</v>
       </c>
-      <c r="C21" s="33" t="n">
+      <c r="C21" s="32" t="n">
         <v>14992</v>
       </c>
-      <c r="D21" s="33" t="n">
+      <c r="D21" s="32" t="n">
         <v>7938</v>
       </c>
-      <c r="E21" s="34" t="n">
+      <c r="E21" s="33" t="n">
         <v>0.46</v>
       </c>
     </row>
@@ -4890,10 +4886,10 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>71423493.52320346</v>
+        <v>107967248.3546386</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>22667647.0547853</v>
+        <v>46355202.65119191</v>
       </c>
     </row>
     <row r="6">
@@ -4903,10 +4899,10 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>58910724.97</v>
+        <v>97631341.61583415</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>18908534.4</v>
+        <v>40564908.19614005</v>
       </c>
     </row>
     <row r="7">
@@ -4916,10 +4912,10 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>143859401.3306556</v>
+        <v>102360063.267196</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>43199234.69200069</v>
+        <v>44668260.26461965</v>
       </c>
     </row>
     <row r="8">
@@ -4929,23 +4925,23 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>141385739.9279986</v>
+        <v>95234846.80000003</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>45380482.55999956</v>
+        <v>39671501.93799989</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>АНСАМБЛЬ (база)</t>
         </is>
       </c>
-      <c r="B9" s="15" t="n">
-        <v>93153136.83697945</v>
-      </c>
-      <c r="C9" s="15" t="n">
-        <v>29350174.13771413</v>
+      <c r="B9" s="14" t="n">
+        <v>101995713.5958934</v>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>43317847.53680471</v>
       </c>
     </row>
   </sheetData>
@@ -4959,7 +4955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4971,8 +4967,6 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5017,32 +5011,22 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Маркет выр.лиды</t>
+          <t>ОФД расход</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>ОФД расход</t>
+          <t>ОФД опл.</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>ОФД опл.</t>
+          <t>ОФД CPO</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>ОФД CPO</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
           <t>ОФД CPL</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>ОФД выр.лиды</t>
         </is>
       </c>
     </row>
@@ -5065,22 +5049,16 @@
         <v>16212</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="6" t="n">
         <v>349519</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="G5" s="5" t="n">
         <v>40</v>
       </c>
+      <c r="H5" s="6" t="n">
+        <v>8738</v>
+      </c>
       <c r="I5" s="6" t="n">
-        <v>8738</v>
-      </c>
-      <c r="J5" s="6" t="n">
         <v>2608</v>
-      </c>
-      <c r="K5" s="6" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -5102,22 +5080,16 @@
         <v>14301</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="6" t="n">
         <v>417835</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="G6" s="5" t="n">
         <v>35</v>
       </c>
+      <c r="H6" s="6" t="n">
+        <v>11938</v>
+      </c>
       <c r="I6" s="6" t="n">
-        <v>11938</v>
-      </c>
-      <c r="J6" s="6" t="n">
         <v>4096</v>
-      </c>
-      <c r="K6" s="6" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -5139,22 +5111,16 @@
         <v>14680</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="6" t="n">
         <v>457771</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="G7" s="5" t="n">
         <v>20</v>
       </c>
+      <c r="H7" s="6" t="n">
+        <v>22889</v>
+      </c>
       <c r="I7" s="6" t="n">
-        <v>22889</v>
-      </c>
-      <c r="J7" s="6" t="n">
         <v>4976</v>
-      </c>
-      <c r="K7" s="6" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -5176,22 +5142,16 @@
         <v>13018</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="6" t="n">
         <v>586537</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="G8" s="5" t="n">
         <v>17</v>
       </c>
+      <c r="H8" s="6" t="n">
+        <v>34502</v>
+      </c>
       <c r="I8" s="6" t="n">
-        <v>34502</v>
-      </c>
-      <c r="J8" s="6" t="n">
         <v>8626</v>
-      </c>
-      <c r="K8" s="6" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -5213,22 +5173,16 @@
         <v>9666</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="6" t="n">
         <v>524111</v>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="G9" s="5" t="n">
         <v>11</v>
       </c>
+      <c r="H9" s="6" t="n">
+        <v>47646</v>
+      </c>
       <c r="I9" s="6" t="n">
-        <v>47646</v>
-      </c>
-      <c r="J9" s="6" t="n">
         <v>10079</v>
-      </c>
-      <c r="K9" s="6" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -5250,22 +5204,16 @@
         <v>8504</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="6" t="n">
         <v>426952</v>
       </c>
-      <c r="H10" s="5" t="n">
+      <c r="G10" s="5" t="n">
         <v>8</v>
       </c>
+      <c r="H10" s="6" t="n">
+        <v>53369</v>
+      </c>
       <c r="I10" s="6" t="n">
-        <v>53369</v>
-      </c>
-      <c r="J10" s="6" t="n">
         <v>9282</v>
-      </c>
-      <c r="K10" s="6" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -5287,22 +5235,16 @@
         <v>6596</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="6" t="n">
         <v>356743</v>
       </c>
-      <c r="H11" s="5" t="n">
+      <c r="G11" s="5" t="n">
         <v>24</v>
       </c>
+      <c r="H11" s="6" t="n">
+        <v>14864</v>
+      </c>
       <c r="I11" s="6" t="n">
-        <v>14864</v>
-      </c>
-      <c r="J11" s="6" t="n">
         <v>4694</v>
-      </c>
-      <c r="K11" s="6" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -5324,22 +5266,16 @@
         <v>8361</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="6" t="n">
         <v>367080</v>
       </c>
-      <c r="H12" s="5" t="n">
+      <c r="G12" s="5" t="n">
         <v>19</v>
       </c>
+      <c r="H12" s="6" t="n">
+        <v>19320</v>
+      </c>
       <c r="I12" s="6" t="n">
-        <v>19320</v>
-      </c>
-      <c r="J12" s="6" t="n">
         <v>4706</v>
-      </c>
-      <c r="K12" s="6" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -5361,22 +5297,16 @@
         <v>8217</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="6" t="n">
         <v>405867</v>
       </c>
-      <c r="H13" s="5" t="n">
+      <c r="G13" s="5" t="n">
         <v>20</v>
       </c>
+      <c r="H13" s="6" t="n">
+        <v>20293</v>
+      </c>
       <c r="I13" s="6" t="n">
-        <v>20293</v>
-      </c>
-      <c r="J13" s="6" t="n">
         <v>4560</v>
-      </c>
-      <c r="K13" s="6" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -5398,22 +5328,16 @@
         <v>11034</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="6" t="n">
         <v>460200</v>
       </c>
-      <c r="H14" s="5" t="n">
+      <c r="G14" s="5" t="n">
         <v>21</v>
       </c>
+      <c r="H14" s="6" t="n">
+        <v>21914</v>
+      </c>
       <c r="I14" s="6" t="n">
-        <v>21914</v>
-      </c>
-      <c r="J14" s="6" t="n">
         <v>5171</v>
-      </c>
-      <c r="K14" s="6" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -5435,22 +5359,16 @@
         <v>11221</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="6" t="n">
         <v>432649</v>
       </c>
-      <c r="H15" s="5" t="n">
+      <c r="G15" s="5" t="n">
         <v>23</v>
       </c>
+      <c r="H15" s="6" t="n">
+        <v>18811</v>
+      </c>
       <c r="I15" s="6" t="n">
-        <v>18811</v>
-      </c>
-      <c r="J15" s="6" t="n">
         <v>4973</v>
-      </c>
-      <c r="K15" s="6" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -5472,22 +5390,16 @@
         <v>9665</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="6" t="n">
         <v>386677</v>
       </c>
-      <c r="H16" s="5" t="n">
+      <c r="G16" s="5" t="n">
         <v>30</v>
       </c>
+      <c r="H16" s="6" t="n">
+        <v>12889</v>
+      </c>
       <c r="I16" s="6" t="n">
-        <v>12889</v>
-      </c>
-      <c r="J16" s="6" t="n">
         <v>3906</v>
-      </c>
-      <c r="K16" s="6" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -5509,22 +5421,16 @@
         <v>7650</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="6" t="n">
         <v>415847</v>
       </c>
-      <c r="H17" s="5" t="n">
+      <c r="G17" s="5" t="n">
         <v>32</v>
       </c>
+      <c r="H17" s="6" t="n">
+        <v>12995</v>
+      </c>
       <c r="I17" s="6" t="n">
-        <v>12995</v>
-      </c>
-      <c r="J17" s="6" t="n">
         <v>3465</v>
-      </c>
-      <c r="K17" s="6" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -5546,22 +5452,16 @@
         <v>9694</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="6" t="n">
         <v>386770</v>
       </c>
-      <c r="H18" s="5" t="n">
+      <c r="G18" s="5" t="n">
         <v>29</v>
       </c>
+      <c r="H18" s="6" t="n">
+        <v>13337</v>
+      </c>
       <c r="I18" s="6" t="n">
-        <v>13337</v>
-      </c>
-      <c r="J18" s="6" t="n">
         <v>3484</v>
-      </c>
-      <c r="K18" s="6" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -5583,22 +5483,16 @@
         <v>10513</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="6" t="n">
         <v>423647</v>
       </c>
-      <c r="H19" s="5" t="n">
+      <c r="G19" s="5" t="n">
         <v>25</v>
       </c>
+      <c r="H19" s="6" t="n">
+        <v>16946</v>
+      </c>
       <c r="I19" s="6" t="n">
-        <v>16946</v>
-      </c>
-      <c r="J19" s="6" t="n">
         <v>3560</v>
-      </c>
-      <c r="K19" s="6" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -5620,22 +5514,16 @@
         <v>5998</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="6" t="n">
         <v>390294</v>
       </c>
-      <c r="H20" s="5" t="n">
+      <c r="G20" s="5" t="n">
         <v>21</v>
       </c>
+      <c r="H20" s="6" t="n">
+        <v>18585</v>
+      </c>
       <c r="I20" s="6" t="n">
-        <v>18585</v>
-      </c>
-      <c r="J20" s="6" t="n">
         <v>3199</v>
-      </c>
-      <c r="K20" s="6" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -5657,22 +5545,16 @@
         <v>4537</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="6" t="n">
         <v>262720</v>
       </c>
-      <c r="H21" s="5" t="n">
+      <c r="G21" s="5" t="n">
         <v>18</v>
       </c>
+      <c r="H21" s="6" t="n">
+        <v>14596</v>
+      </c>
       <c r="I21" s="6" t="n">
-        <v>14596</v>
-      </c>
-      <c r="J21" s="6" t="n">
         <v>4042</v>
-      </c>
-      <c r="K21" s="6" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -5694,22 +5576,16 @@
         <v>4608</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="6" t="n">
         <v>52264</v>
       </c>
-      <c r="H22" s="5" t="n">
+      <c r="G22" s="5" t="n">
         <v>4</v>
       </c>
+      <c r="H22" s="6" t="n">
+        <v>13066</v>
+      </c>
       <c r="I22" s="6" t="n">
-        <v>13066</v>
-      </c>
-      <c r="J22" s="6" t="n">
         <v>1936</v>
-      </c>
-      <c r="K22" s="6" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Прогноз 2026 — Маркет и ОФД (с лидами).xlsx
+++ b/Прогноз 2026 — Маркет и ОФД (с лидами).xlsx
@@ -30,7 +30,7 @@
     <numFmt numFmtId="164" formatCode="#,##0 ₽"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -76,34 +76,16 @@
     <font>
       <name val="Montserrat"/>
       <b val="1"/>
-      <color rgb="001D2430"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Montserrat"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Montserrat"/>
       <b val="1"/>
-      <color rgb="005E6670"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Montserrat"/>
-      <b val="1"/>
-      <color rgb="001D2430"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <name val="Montserrat"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Montserrat"/>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Montserrat"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -151,7 +133,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -183,19 +165,13 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="12" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="12" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="10" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -274,6 +250,7 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
   <chart>
     <title>
       <tx>
@@ -284,7 +261,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Маркет: план / факт / прогноз</a:t>
+              <a:t>Маркет: план / факт / прогноз — выручка, ₽</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -302,14 +279,24 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
+              <a:solidFill>
+                <a:srgbClr val="C2C8D0"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="none"/>
+            <symbol val="circle"/>
+            <size val="5"/>
             <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="C2C8D0"/>
+              </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="C2C8D0"/>
+                </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -324,56 +311,35 @@
               <f>'Маркет (выручка)'!$B$5:$B$16</f>
             </numRef>
           </val>
+          <smooth val="0"/>
         </ser>
         <ser>
           <idx val="1"/>
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Маркет (выручка)'!C4</f>
+              <f>'Маркет (выручка)'!D4</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
+              <a:solidFill>
+                <a:srgbClr val="2291FF"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="none"/>
+            <symbol val="circle"/>
+            <size val="5"/>
             <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="2291FF"/>
+              </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Маркет (выручка)'!$A$5:$A$16</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Маркет (выручка)'!$C$5:$C$16</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="2"/>
-          <order val="2"/>
-          <tx>
-            <strRef>
-              <f>'Маркет (выручка)'!D4</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="2291FF"/>
+                </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -388,24 +354,35 @@
               <f>'Маркет (выручка)'!$D$5:$D$16</f>
             </numRef>
           </val>
+          <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="3"/>
-          <order val="3"/>
+          <idx val="2"/>
+          <order val="2"/>
           <tx>
             <strRef>
               <f>'Маркет (выручка)'!E4</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
+              <a:solidFill>
+                <a:srgbClr val="153177"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="none"/>
+            <symbol val="circle"/>
+            <size val="5"/>
             <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="153177"/>
+              </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="153177"/>
+                </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -420,71 +397,9 @@
               <f>'Маркет (выручка)'!$E$5:$E$16</f>
             </numRef>
           </val>
+          <smooth val="0"/>
         </ser>
-        <ser>
-          <idx val="4"/>
-          <order val="4"/>
-          <tx>
-            <strRef>
-              <f>'Маркет (выручка)'!F4</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Маркет (выручка)'!$A$5:$A$16</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Маркет (выручка)'!$F$5:$F$16</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="5"/>
-          <order val="5"/>
-          <tx>
-            <strRef>
-              <f>'Маркет (выручка)'!G4</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Маркет (выручка)'!$A$5:$A$16</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Маркет (выручка)'!$G$5:$G$16</f>
-            </numRef>
-          </val>
-        </ser>
+        <smooth val="0"/>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -493,9 +408,11 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -504,15 +421,17 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -522,6 +441,7 @@
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
   <chart>
     <title>
       <tx>
@@ -532,7 +452,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Маркет: план / факт / прогноз</a:t>
+              <a:t>Маркет: план / факт / прогноз — оплаты, шт</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -550,14 +470,24 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
+              <a:solidFill>
+                <a:srgbClr val="C2C8D0"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="none"/>
+            <symbol val="circle"/>
+            <size val="5"/>
             <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="C2C8D0"/>
+              </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="C2C8D0"/>
+                </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -572,56 +502,35 @@
               <f>'Маркет (оплаты)'!$B$5:$B$16</f>
             </numRef>
           </val>
+          <smooth val="0"/>
         </ser>
         <ser>
           <idx val="1"/>
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Маркет (оплаты)'!C4</f>
+              <f>'Маркет (оплаты)'!D4</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
+              <a:solidFill>
+                <a:srgbClr val="2291FF"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="none"/>
+            <symbol val="circle"/>
+            <size val="5"/>
             <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="2291FF"/>
+              </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Маркет (оплаты)'!$A$5:$A$16</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Маркет (оплаты)'!$C$5:$C$16</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="2"/>
-          <order val="2"/>
-          <tx>
-            <strRef>
-              <f>'Маркет (оплаты)'!D4</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="2291FF"/>
+                </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -636,24 +545,35 @@
               <f>'Маркет (оплаты)'!$D$5:$D$16</f>
             </numRef>
           </val>
+          <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="3"/>
-          <order val="3"/>
+          <idx val="2"/>
+          <order val="2"/>
           <tx>
             <strRef>
               <f>'Маркет (оплаты)'!E4</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
+              <a:solidFill>
+                <a:srgbClr val="153177"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="none"/>
+            <symbol val="circle"/>
+            <size val="5"/>
             <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="153177"/>
+              </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="153177"/>
+                </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -668,71 +588,9 @@
               <f>'Маркет (оплаты)'!$E$5:$E$16</f>
             </numRef>
           </val>
+          <smooth val="0"/>
         </ser>
-        <ser>
-          <idx val="4"/>
-          <order val="4"/>
-          <tx>
-            <strRef>
-              <f>'Маркет (оплаты)'!F4</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Маркет (оплаты)'!$A$5:$A$16</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Маркет (оплаты)'!$F$5:$F$16</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="5"/>
-          <order val="5"/>
-          <tx>
-            <strRef>
-              <f>'Маркет (оплаты)'!G4</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Маркет (оплаты)'!$A$5:$A$16</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Маркет (оплаты)'!$G$5:$G$16</f>
-            </numRef>
-          </val>
-        </ser>
+        <smooth val="0"/>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -741,9 +599,11 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -752,15 +612,17 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -770,6 +632,7 @@
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
   <chart>
     <title>
       <tx>
@@ -780,7 +643,198 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>ОФД: план / факт / прогноз</a:t>
+              <a:t>Маркет: план / факт / прогноз — лиды, шт</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Маркет (лиды)'!B4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
+              <a:solidFill>
+                <a:srgbClr val="C2C8D0"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="5"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="C2C8D0"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="C2C8D0"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Маркет (лиды)'!$A$5:$A$16</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Маркет (лиды)'!$B$5:$B$16</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Маркет (лиды)'!D4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
+              <a:solidFill>
+                <a:srgbClr val="2291FF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="5"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="2291FF"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="2291FF"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Маркет (лиды)'!$A$5:$A$16</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Маркет (лиды)'!$D$5:$D$16</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Маркет (лиды)'!E4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
+              <a:solidFill>
+                <a:srgbClr val="153177"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="5"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="153177"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="153177"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Маркет (лиды)'!$A$5:$A$16</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Маркет (лиды)'!$E$5:$E$16</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <smooth val="0"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>ОФД: план / факт / прогноз — выручка, ₽</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -798,14 +852,24 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
+              <a:solidFill>
+                <a:srgbClr val="C2C8D0"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="none"/>
+            <symbol val="circle"/>
+            <size val="5"/>
             <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="C2C8D0"/>
+              </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="C2C8D0"/>
+                </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -820,56 +884,35 @@
               <f>'ОФД (выручка)'!$B$5:$B$16</f>
             </numRef>
           </val>
+          <smooth val="0"/>
         </ser>
         <ser>
           <idx val="1"/>
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'ОФД (выручка)'!C4</f>
+              <f>'ОФД (выручка)'!D4</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
+              <a:solidFill>
+                <a:srgbClr val="2291FF"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="none"/>
+            <symbol val="circle"/>
+            <size val="5"/>
             <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="2291FF"/>
+              </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'ОФД (выручка)'!$A$5:$A$16</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'ОФД (выручка)'!$C$5:$C$16</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="2"/>
-          <order val="2"/>
-          <tx>
-            <strRef>
-              <f>'ОФД (выручка)'!D4</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="2291FF"/>
+                </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -884,24 +927,35 @@
               <f>'ОФД (выручка)'!$D$5:$D$16</f>
             </numRef>
           </val>
+          <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="3"/>
-          <order val="3"/>
+          <idx val="2"/>
+          <order val="2"/>
           <tx>
             <strRef>
               <f>'ОФД (выручка)'!E4</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
+              <a:solidFill>
+                <a:srgbClr val="153177"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="none"/>
+            <symbol val="circle"/>
+            <size val="5"/>
             <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="153177"/>
+              </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="153177"/>
+                </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -916,71 +970,9 @@
               <f>'ОФД (выручка)'!$E$5:$E$16</f>
             </numRef>
           </val>
+          <smooth val="0"/>
         </ser>
-        <ser>
-          <idx val="4"/>
-          <order val="4"/>
-          <tx>
-            <strRef>
-              <f>'ОФД (выручка)'!F4</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'ОФД (выручка)'!$A$5:$A$16</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'ОФД (выручка)'!$F$5:$F$16</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="5"/>
-          <order val="5"/>
-          <tx>
-            <strRef>
-              <f>'ОФД (выручка)'!G4</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'ОФД (выручка)'!$A$5:$A$16</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'ОФД (выручка)'!$G$5:$G$16</f>
-            </numRef>
-          </val>
-        </ser>
+        <smooth val="0"/>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -989,9 +981,11 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -1000,15 +994,17 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -1016,8 +1012,9 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
   <chart>
     <title>
       <tx>
@@ -1028,7 +1025,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>ОФД: план / факт / прогноз</a:t>
+              <a:t>ОФД: план / факт / прогноз — оплаты, шт</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1046,14 +1043,24 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
+              <a:solidFill>
+                <a:srgbClr val="C2C8D0"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="none"/>
+            <symbol val="circle"/>
+            <size val="5"/>
             <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="C2C8D0"/>
+              </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="C2C8D0"/>
+                </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1068,56 +1075,35 @@
               <f>'ОФД (оплаты)'!$B$5:$B$16</f>
             </numRef>
           </val>
+          <smooth val="0"/>
         </ser>
         <ser>
           <idx val="1"/>
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'ОФД (оплаты)'!C4</f>
+              <f>'ОФД (оплаты)'!D4</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
+              <a:solidFill>
+                <a:srgbClr val="2291FF"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="none"/>
+            <symbol val="circle"/>
+            <size val="5"/>
             <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="2291FF"/>
+              </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'ОФД (оплаты)'!$A$5:$A$16</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'ОФД (оплаты)'!$C$5:$C$16</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="2"/>
-          <order val="2"/>
-          <tx>
-            <strRef>
-              <f>'ОФД (оплаты)'!D4</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="2291FF"/>
+                </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1132,24 +1118,35 @@
               <f>'ОФД (оплаты)'!$D$5:$D$16</f>
             </numRef>
           </val>
+          <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="3"/>
-          <order val="3"/>
+          <idx val="2"/>
+          <order val="2"/>
           <tx>
             <strRef>
               <f>'ОФД (оплаты)'!E4</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
+              <a:solidFill>
+                <a:srgbClr val="153177"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="none"/>
+            <symbol val="circle"/>
+            <size val="5"/>
             <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="153177"/>
+              </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="153177"/>
+                </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1164,71 +1161,9 @@
               <f>'ОФД (оплаты)'!$E$5:$E$16</f>
             </numRef>
           </val>
+          <smooth val="0"/>
         </ser>
-        <ser>
-          <idx val="4"/>
-          <order val="4"/>
-          <tx>
-            <strRef>
-              <f>'ОФД (оплаты)'!F4</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'ОФД (оплаты)'!$A$5:$A$16</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'ОФД (оплаты)'!$F$5:$F$16</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="5"/>
-          <order val="5"/>
-          <tx>
-            <strRef>
-              <f>'ОФД (оплаты)'!G4</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'ОФД (оплаты)'!$A$5:$A$16</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'ОФД (оплаты)'!$G$5:$G$16</f>
-            </numRef>
-          </val>
-        </ser>
+        <smooth val="0"/>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -1237,9 +1172,11 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -1248,15 +1185,208 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>ОФД: план / факт / прогноз — лиды, шт</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'ОФД (лиды)'!B4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
+              <a:solidFill>
+                <a:srgbClr val="C2C8D0"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="5"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="C2C8D0"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="C2C8D0"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'ОФД (лиды)'!$A$5:$A$16</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'ОФД (лиды)'!$B$5:$B$16</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'ОФД (лиды)'!D4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
+              <a:solidFill>
+                <a:srgbClr val="2291FF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="5"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="2291FF"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="2291FF"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'ОФД (лиды)'!$A$5:$A$16</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'ОФД (лиды)'!$D$5:$D$16</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'ОФД (лиды)'!E4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
+              <a:solidFill>
+                <a:srgbClr val="153177"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="5"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="153177"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="153177"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'ОФД (лиды)'!$A$5:$A$16</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'ОФД (лиды)'!$E$5:$E$16</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <smooth val="0"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -1273,7 +1403,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7200000" cy="3240000"/>
+    <ext cx="8640000" cy="2951999"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1300,7 +1430,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7200000" cy="3240000"/>
+    <ext cx="8640000" cy="2951999"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1327,7 +1457,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7200000" cy="3240000"/>
+    <ext cx="8640000" cy="2951999"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1354,7 +1484,61 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7200000" cy="3240000"/>
+    <ext cx="8640000" cy="2951999"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="2951999"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="2951999"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -3412,357 +3596,351 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="inlineStr">
         <is>
-          <t>Маркет — лиды 2026, помесячно (прогноз)</t>
+          <t>Маркет — лиды 2026, помесячно (мой прогноз = оплаты ÷ CR2)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="22" t="inlineStr">
         <is>
-          <t>Источник: ГЭП-анализ · CR2 лид→оплата = 36%</t>
+          <t>CR2 лид→оплата = 36% · лиды пересчитаны из модельного прогноза оплат (ансамбль)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="23" t="inlineStr">
         <is>
-          <t>Годовой прогноз</t>
+          <t>Месяц</t>
+        </is>
+      </c>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>План 2026</t>
+        </is>
+      </c>
+      <c r="C4" s="23" t="inlineStr">
+        <is>
+          <t>Факт 2025</t>
+        </is>
+      </c>
+      <c r="D4" s="23" t="inlineStr">
+        <is>
+          <t>Факт 2026</t>
+        </is>
+      </c>
+      <c r="E4" s="23" t="inlineStr">
+        <is>
+          <t>Прогноз база</t>
+        </is>
+      </c>
+      <c r="F4" s="23" t="inlineStr">
+        <is>
+          <t>Прогноз низ</t>
+        </is>
+      </c>
+      <c r="G4" s="23" t="inlineStr">
+        <is>
+          <t>Прогноз верх</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="24" t="inlineStr">
         <is>
-          <t>Лиды прогноз</t>
-        </is>
-      </c>
-      <c r="B5" s="24" t="inlineStr">
-        <is>
-          <t>Нужно лидов для плана</t>
-        </is>
-      </c>
-      <c r="C5" s="24" t="inlineStr">
-        <is>
-          <t>Выполнение по лидам</t>
-        </is>
-      </c>
-      <c r="D5" s="24" t="inlineStr">
-        <is>
-          <t>Оплаты прогноз</t>
-        </is>
-      </c>
-      <c r="E5" s="24" t="inlineStr">
-        <is>
-          <t>CR2</t>
-        </is>
-      </c>
+          <t>Январь</t>
+        </is>
+      </c>
+      <c r="B5" s="25" t="n">
+        <v>1714</v>
+      </c>
+      <c r="C5" s="25" t="n">
+        <v>2089</v>
+      </c>
+      <c r="D5" s="25" t="n">
+        <v>1325</v>
+      </c>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="25" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="25" t="n">
-        <v>20471</v>
+      <c r="A6" s="24" t="inlineStr">
+        <is>
+          <t>Февраль</t>
+        </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>23758</v>
-      </c>
-      <c r="C6" s="26" t="n">
-        <v>0.8616466032494318</v>
+        <v>1478</v>
+      </c>
+      <c r="C6" s="25" t="n">
+        <v>1789</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>7310</v>
-      </c>
-      <c r="E6" s="26" t="n">
-        <v>0.36</v>
-      </c>
+        <v>1392</v>
+      </c>
+      <c r="E6" s="25" t="n"/>
+      <c r="F6" s="25" t="n"/>
+      <c r="G6" s="25" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="24" t="inlineStr">
+        <is>
+          <t>Март</t>
+        </is>
+      </c>
+      <c r="B7" s="25" t="n">
+        <v>1667</v>
+      </c>
+      <c r="C7" s="25" t="n">
+        <v>1961</v>
+      </c>
+      <c r="D7" s="25" t="n">
+        <v>1667</v>
+      </c>
+      <c r="E7" s="25" t="n"/>
+      <c r="F7" s="25" t="n"/>
+      <c r="G7" s="25" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="inlineStr">
-        <is>
-          <t>Месяц</t>
-        </is>
-      </c>
-      <c r="B8" s="27" t="inlineStr">
-        <is>
-          <t>Лиды (прогноз)</t>
-        </is>
-      </c>
-      <c r="C8" s="27" t="inlineStr">
-        <is>
-          <t>Нужно лидов для плана</t>
-        </is>
-      </c>
-      <c r="D8" s="27" t="inlineStr">
-        <is>
-          <t>Оплаты (прогноз)</t>
-        </is>
-      </c>
-      <c r="E8" s="27" t="inlineStr">
-        <is>
-          <t>CR2</t>
-        </is>
-      </c>
+      <c r="A8" s="24" t="inlineStr">
+        <is>
+          <t>Апрель</t>
+        </is>
+      </c>
+      <c r="B8" s="25" t="n">
+        <v>1600</v>
+      </c>
+      <c r="C8" s="25" t="n">
+        <v>2453</v>
+      </c>
+      <c r="D8" s="25" t="n">
+        <v>1325</v>
+      </c>
+      <c r="E8" s="25" t="n"/>
+      <c r="F8" s="25" t="n"/>
+      <c r="G8" s="25" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="28" t="inlineStr">
-        <is>
-          <t>Январь</t>
-        </is>
-      </c>
-      <c r="B9" s="29" t="n">
-        <v>1647</v>
-      </c>
-      <c r="C9" s="29" t="n">
-        <v>1812</v>
-      </c>
-      <c r="D9" s="29" t="n">
-        <v>573</v>
-      </c>
-      <c r="E9" s="30" t="n">
-        <v>0.36</v>
-      </c>
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>Май</t>
+        </is>
+      </c>
+      <c r="B9" s="25" t="n">
+        <v>1144</v>
+      </c>
+      <c r="C9" s="25" t="n">
+        <v>1703</v>
+      </c>
+      <c r="D9" s="25" t="n">
+        <v>1119</v>
+      </c>
+      <c r="E9" s="25" t="n"/>
+      <c r="F9" s="25" t="n"/>
+      <c r="G9" s="25" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="28" t="inlineStr">
-        <is>
-          <t>Февраль</t>
-        </is>
-      </c>
-      <c r="B10" s="29" t="n">
-        <v>1736</v>
-      </c>
-      <c r="C10" s="29" t="n">
-        <v>1910</v>
-      </c>
-      <c r="D10" s="29" t="n">
-        <v>605</v>
-      </c>
-      <c r="E10" s="30" t="n">
-        <v>0.36</v>
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>Июнь</t>
+        </is>
+      </c>
+      <c r="B10" s="25" t="n">
+        <v>1461</v>
+      </c>
+      <c r="C10" s="25" t="n">
+        <v>1944</v>
+      </c>
+      <c r="D10" s="25" t="n"/>
+      <c r="E10" s="25" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F10" s="25" t="n">
+        <v>1283</v>
+      </c>
+      <c r="G10" s="25" t="n">
+        <v>1328</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="28" t="inlineStr">
-        <is>
-          <t>Март</t>
-        </is>
-      </c>
-      <c r="B11" s="29" t="n">
-        <v>1881</v>
-      </c>
-      <c r="C11" s="29" t="n">
-        <v>2069</v>
-      </c>
-      <c r="D11" s="29" t="n">
-        <v>657</v>
-      </c>
-      <c r="E11" s="30" t="n">
-        <v>0.36</v>
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>Июль</t>
+        </is>
+      </c>
+      <c r="B11" s="25" t="n">
+        <v>1561</v>
+      </c>
+      <c r="C11" s="25" t="n">
+        <v>1622</v>
+      </c>
+      <c r="D11" s="25" t="n"/>
+      <c r="E11" s="25" t="n">
+        <v>1225</v>
+      </c>
+      <c r="F11" s="25" t="n">
+        <v>989</v>
+      </c>
+      <c r="G11" s="25" t="n">
+        <v>1402</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="28" t="inlineStr">
-        <is>
-          <t>Апрель</t>
-        </is>
-      </c>
-      <c r="B12" s="29" t="n">
-        <v>1822</v>
-      </c>
-      <c r="C12" s="29" t="n">
-        <v>2004</v>
-      </c>
-      <c r="D12" s="29" t="n">
-        <v>656</v>
-      </c>
-      <c r="E12" s="30" t="n">
-        <v>0.36</v>
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>Август</t>
+        </is>
+      </c>
+      <c r="B12" s="25" t="n">
+        <v>1272</v>
+      </c>
+      <c r="C12" s="25" t="n">
+        <v>1272</v>
+      </c>
+      <c r="D12" s="25" t="n"/>
+      <c r="E12" s="25" t="n">
+        <v>988</v>
+      </c>
+      <c r="F12" s="25" t="n">
+        <v>639</v>
+      </c>
+      <c r="G12" s="25" t="n">
+        <v>1243</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="28" t="inlineStr">
-        <is>
-          <t>Май</t>
-        </is>
-      </c>
-      <c r="B13" s="29" t="n">
-        <v>1772</v>
-      </c>
-      <c r="C13" s="29" t="n">
-        <v>2215</v>
-      </c>
-      <c r="D13" s="29" t="n">
-        <v>638</v>
-      </c>
-      <c r="E13" s="30" t="n">
-        <v>0.36</v>
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>Сентябрь</t>
+        </is>
+      </c>
+      <c r="B13" s="25" t="n">
+        <v>1325</v>
+      </c>
+      <c r="C13" s="25" t="n">
+        <v>1436</v>
+      </c>
+      <c r="D13" s="25" t="n"/>
+      <c r="E13" s="25" t="n">
+        <v>1066</v>
+      </c>
+      <c r="F13" s="25" t="n">
+        <v>803</v>
+      </c>
+      <c r="G13" s="25" t="n">
+        <v>1225</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="28" t="inlineStr">
-        <is>
-          <t>Июнь</t>
-        </is>
-      </c>
-      <c r="B14" s="29" t="n">
-        <v>1594</v>
-      </c>
-      <c r="C14" s="29" t="n">
-        <v>1993</v>
-      </c>
-      <c r="D14" s="29" t="n">
-        <v>574</v>
-      </c>
-      <c r="E14" s="30" t="n">
-        <v>0.36</v>
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>Октябрь</t>
+        </is>
+      </c>
+      <c r="B14" s="25" t="n">
+        <v>1553</v>
+      </c>
+      <c r="C14" s="25" t="n">
+        <v>1469</v>
+      </c>
+      <c r="D14" s="25" t="n"/>
+      <c r="E14" s="25" t="n">
+        <v>1157</v>
+      </c>
+      <c r="F14" s="25" t="n">
+        <v>836</v>
+      </c>
+      <c r="G14" s="25" t="n">
+        <v>1394</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="28" t="inlineStr">
-        <is>
-          <t>Июль</t>
-        </is>
-      </c>
-      <c r="B15" s="29" t="n">
-        <v>1611</v>
-      </c>
-      <c r="C15" s="29" t="n">
-        <v>2014</v>
-      </c>
-      <c r="D15" s="29" t="n">
-        <v>580</v>
-      </c>
-      <c r="E15" s="30" t="n">
-        <v>0.36</v>
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>Ноябрь</t>
+        </is>
+      </c>
+      <c r="B15" s="25" t="n">
+        <v>1358</v>
+      </c>
+      <c r="C15" s="25" t="n">
+        <v>1267</v>
+      </c>
+      <c r="D15" s="25" t="n"/>
+      <c r="E15" s="25" t="n">
+        <v>1010</v>
+      </c>
+      <c r="F15" s="25" t="n">
+        <v>633</v>
+      </c>
+      <c r="G15" s="25" t="n">
+        <v>1220</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="28" t="inlineStr">
-        <is>
-          <t>Август</t>
-        </is>
-      </c>
-      <c r="B16" s="29" t="n">
-        <v>1631</v>
-      </c>
-      <c r="C16" s="29" t="n">
-        <v>1794</v>
-      </c>
-      <c r="D16" s="29" t="n">
-        <v>587</v>
-      </c>
-      <c r="E16" s="30" t="n">
-        <v>0.36</v>
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>Декабрь</t>
+        </is>
+      </c>
+      <c r="B16" s="25" t="n">
+        <v>1642</v>
+      </c>
+      <c r="C16" s="25" t="n">
+        <v>1869</v>
+      </c>
+      <c r="D16" s="25" t="n"/>
+      <c r="E16" s="25" t="n">
+        <v>1333</v>
+      </c>
+      <c r="F16" s="25" t="n">
+        <v>1181</v>
+      </c>
+      <c r="G16" s="25" t="n">
+        <v>1474</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="28" t="inlineStr">
-        <is>
-          <t>Сентябрь</t>
-        </is>
-      </c>
-      <c r="B17" s="29" t="n">
-        <v>1586</v>
-      </c>
-      <c r="C17" s="29" t="n">
-        <v>1745</v>
-      </c>
-      <c r="D17" s="29" t="n">
-        <v>571</v>
-      </c>
-      <c r="E17" s="30" t="n">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="28" t="inlineStr">
-        <is>
-          <t>Октябрь</t>
-        </is>
-      </c>
-      <c r="B18" s="29" t="n">
-        <v>1719</v>
-      </c>
-      <c r="C18" s="29" t="n">
-        <v>1891</v>
-      </c>
-      <c r="D18" s="29" t="n">
-        <v>619</v>
-      </c>
-      <c r="E18" s="30" t="n">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="28" t="inlineStr">
-        <is>
-          <t>Ноябрь</t>
-        </is>
-      </c>
-      <c r="B19" s="29" t="n">
-        <v>1836</v>
-      </c>
-      <c r="C19" s="29" t="n">
-        <v>2020</v>
-      </c>
-      <c r="D19" s="29" t="n">
-        <v>661</v>
-      </c>
-      <c r="E19" s="30" t="n">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="28" t="inlineStr">
-        <is>
-          <t>Декабрь</t>
-        </is>
-      </c>
-      <c r="B20" s="29" t="n">
-        <v>1636</v>
-      </c>
-      <c r="C20" s="29" t="n">
-        <v>2291</v>
-      </c>
-      <c r="D20" s="29" t="n">
-        <v>589</v>
-      </c>
-      <c r="E20" s="30" t="n">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="31" t="inlineStr">
-        <is>
-          <t>Итого 2026</t>
-        </is>
-      </c>
-      <c r="B21" s="32" t="n">
-        <v>20471</v>
-      </c>
-      <c r="C21" s="32" t="n">
-        <v>23758</v>
-      </c>
-      <c r="D21" s="32" t="n">
-        <v>7310</v>
-      </c>
-      <c r="E21" s="33" t="n">
-        <v>0.36</v>
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>ИТОГО год</t>
+        </is>
+      </c>
+      <c r="B17" s="27" t="n">
+        <v>17775</v>
+      </c>
+      <c r="C17" s="27" t="n"/>
+      <c r="D17" s="27" t="n">
+        <v>6828</v>
+      </c>
+      <c r="E17" s="27" t="n">
+        <v>14919</v>
+      </c>
+      <c r="F17" s="27" t="n">
+        <v>13192</v>
+      </c>
+      <c r="G17" s="27" t="n">
+        <v>16115</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4480,357 +4658,351 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="inlineStr">
         <is>
-          <t>ОФД — лиды 2026, помесячно (прогноз)</t>
+          <t>ОФД — лиды 2026, помесячно (мой прогноз = оплаты ÷ CR2)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="22" t="inlineStr">
         <is>
-          <t>Источник: ГЭП-анализ · CR2 лид→оплата = 46%</t>
+          <t>CR2 лид→оплата = 46% · лиды пересчитаны из модельного прогноза оплат (ансамбль)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="23" t="inlineStr">
         <is>
-          <t>Годовой прогноз</t>
+          <t>Месяц</t>
+        </is>
+      </c>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>План 2026</t>
+        </is>
+      </c>
+      <c r="C4" s="23" t="inlineStr">
+        <is>
+          <t>Факт 2025</t>
+        </is>
+      </c>
+      <c r="D4" s="23" t="inlineStr">
+        <is>
+          <t>Факт 2026</t>
+        </is>
+      </c>
+      <c r="E4" s="23" t="inlineStr">
+        <is>
+          <t>Прогноз база</t>
+        </is>
+      </c>
+      <c r="F4" s="23" t="inlineStr">
+        <is>
+          <t>Прогноз низ</t>
+        </is>
+      </c>
+      <c r="G4" s="23" t="inlineStr">
+        <is>
+          <t>Прогноз верх</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="24" t="inlineStr">
         <is>
-          <t>Лиды прогноз</t>
-        </is>
-      </c>
-      <c r="B5" s="24" t="inlineStr">
-        <is>
-          <t>Минимум лидов для плана</t>
-        </is>
-      </c>
-      <c r="C5" s="24" t="inlineStr">
-        <is>
-          <t>Выполнение по лидам</t>
-        </is>
-      </c>
-      <c r="D5" s="24" t="inlineStr">
-        <is>
-          <t>Оплаты прогноз</t>
-        </is>
-      </c>
-      <c r="E5" s="24" t="inlineStr">
-        <is>
-          <t>CR2</t>
-        </is>
-      </c>
+          <t>Январь</t>
+        </is>
+      </c>
+      <c r="B5" s="25" t="n">
+        <v>1202</v>
+      </c>
+      <c r="C5" s="25" t="n">
+        <v>2011</v>
+      </c>
+      <c r="D5" s="25" t="n">
+        <v>1548</v>
+      </c>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="25" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="25" t="n">
-        <v>17196</v>
+      <c r="A6" s="24" t="inlineStr">
+        <is>
+          <t>Февраль</t>
+        </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>14992</v>
-      </c>
-      <c r="C6" s="26" t="n">
-        <v>1.14701173959445</v>
+        <v>1329</v>
+      </c>
+      <c r="C6" s="25" t="n">
+        <v>1739</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>7938</v>
-      </c>
-      <c r="E6" s="26" t="n">
-        <v>0.46</v>
-      </c>
+        <v>1520</v>
+      </c>
+      <c r="E6" s="25" t="n"/>
+      <c r="F6" s="25" t="n"/>
+      <c r="G6" s="25" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="24" t="inlineStr">
+        <is>
+          <t>Март</t>
+        </is>
+      </c>
+      <c r="B7" s="25" t="n">
+        <v>1351</v>
+      </c>
+      <c r="C7" s="25" t="n">
+        <v>1707</v>
+      </c>
+      <c r="D7" s="25" t="n">
+        <v>1546</v>
+      </c>
+      <c r="E7" s="25" t="n"/>
+      <c r="F7" s="25" t="n"/>
+      <c r="G7" s="25" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="inlineStr">
-        <is>
-          <t>Месяц</t>
-        </is>
-      </c>
-      <c r="B8" s="27" t="inlineStr">
-        <is>
-          <t>Лиды (прогноз)</t>
-        </is>
-      </c>
-      <c r="C8" s="27" t="inlineStr">
-        <is>
-          <t>Минимум лидов для плана</t>
-        </is>
-      </c>
-      <c r="D8" s="27" t="inlineStr">
-        <is>
-          <t>Оплаты (прогноз)</t>
-        </is>
-      </c>
-      <c r="E8" s="27" t="inlineStr">
-        <is>
-          <t>CR2</t>
-        </is>
-      </c>
+      <c r="A8" s="24" t="inlineStr">
+        <is>
+          <t>Апрель</t>
+        </is>
+      </c>
+      <c r="B8" s="25" t="n">
+        <v>1386</v>
+      </c>
+      <c r="C8" s="25" t="n">
+        <v>2202</v>
+      </c>
+      <c r="D8" s="25" t="n">
+        <v>1252</v>
+      </c>
+      <c r="E8" s="25" t="n"/>
+      <c r="F8" s="25" t="n"/>
+      <c r="G8" s="25" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="28" t="inlineStr">
-        <is>
-          <t>Январь</t>
-        </is>
-      </c>
-      <c r="B9" s="29" t="n">
-        <v>1326</v>
-      </c>
-      <c r="C9" s="29" t="n">
-        <v>1083</v>
-      </c>
-      <c r="D9" s="29" t="n">
-        <v>613</v>
-      </c>
-      <c r="E9" s="30" t="n">
-        <v>0.46</v>
-      </c>
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>Май</t>
+        </is>
+      </c>
+      <c r="B9" s="25" t="n">
+        <v>1271</v>
+      </c>
+      <c r="C9" s="25" t="n">
+        <v>1883</v>
+      </c>
+      <c r="D9" s="25" t="n">
+        <v>1063</v>
+      </c>
+      <c r="E9" s="25" t="n"/>
+      <c r="F9" s="25" t="n"/>
+      <c r="G9" s="25" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="28" t="inlineStr">
-        <is>
-          <t>Февраль</t>
-        </is>
-      </c>
-      <c r="B10" s="29" t="n">
-        <v>1439</v>
-      </c>
-      <c r="C10" s="29" t="n">
-        <v>1294</v>
-      </c>
-      <c r="D10" s="29" t="n">
-        <v>664</v>
-      </c>
-      <c r="E10" s="30" t="n">
-        <v>0.46</v>
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>Июнь</t>
+        </is>
+      </c>
+      <c r="B10" s="25" t="n">
+        <v>1300</v>
+      </c>
+      <c r="C10" s="25" t="n">
+        <v>1578</v>
+      </c>
+      <c r="D10" s="25" t="n"/>
+      <c r="E10" s="25" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F10" s="25" t="n">
+        <v>1056</v>
+      </c>
+      <c r="G10" s="25" t="n">
+        <v>1377</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="28" t="inlineStr">
-        <is>
-          <t>Март</t>
-        </is>
-      </c>
-      <c r="B11" s="29" t="n">
-        <v>1460</v>
-      </c>
-      <c r="C11" s="29" t="n">
-        <v>1182</v>
-      </c>
-      <c r="D11" s="29" t="n">
-        <v>674</v>
-      </c>
-      <c r="E11" s="30" t="n">
-        <v>0.46</v>
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>Июль</t>
+        </is>
+      </c>
+      <c r="B11" s="25" t="n">
+        <v>1293</v>
+      </c>
+      <c r="C11" s="25" t="n">
+        <v>1363</v>
+      </c>
+      <c r="D11" s="25" t="n"/>
+      <c r="E11" s="25" t="n">
+        <v>1162</v>
+      </c>
+      <c r="F11" s="25" t="n">
+        <v>840</v>
+      </c>
+      <c r="G11" s="25" t="n">
+        <v>1369</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="28" t="inlineStr">
-        <is>
-          <t>Апрель</t>
-        </is>
-      </c>
-      <c r="B12" s="29" t="n">
-        <v>1393</v>
-      </c>
-      <c r="C12" s="29" t="n">
-        <v>1194</v>
-      </c>
-      <c r="D12" s="29" t="n">
-        <v>643</v>
-      </c>
-      <c r="E12" s="30" t="n">
-        <v>0.46</v>
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>Август</t>
+        </is>
+      </c>
+      <c r="B12" s="25" t="n">
+        <v>1272</v>
+      </c>
+      <c r="C12" s="25" t="n">
+        <v>1274</v>
+      </c>
+      <c r="D12" s="25" t="n"/>
+      <c r="E12" s="25" t="n">
+        <v>1119</v>
+      </c>
+      <c r="F12" s="25" t="n">
+        <v>751</v>
+      </c>
+      <c r="G12" s="25" t="n">
+        <v>1347</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="28" t="inlineStr">
-        <is>
-          <t>Май</t>
-        </is>
-      </c>
-      <c r="B13" s="29" t="n">
-        <v>1452</v>
-      </c>
-      <c r="C13" s="29" t="n">
-        <v>1193</v>
-      </c>
-      <c r="D13" s="29" t="n">
-        <v>670</v>
-      </c>
-      <c r="E13" s="30" t="n">
-        <v>0.46</v>
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>Сентябрь</t>
+        </is>
+      </c>
+      <c r="B13" s="25" t="n">
+        <v>1246</v>
+      </c>
+      <c r="C13" s="25" t="n">
+        <v>1220</v>
+      </c>
+      <c r="D13" s="25" t="n"/>
+      <c r="E13" s="25" t="n">
+        <v>1086</v>
+      </c>
+      <c r="F13" s="25" t="n">
+        <v>697</v>
+      </c>
+      <c r="G13" s="25" t="n">
+        <v>1320</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="28" t="inlineStr">
-        <is>
-          <t>Июнь</t>
-        </is>
-      </c>
-      <c r="B14" s="29" t="n">
-        <v>1345</v>
-      </c>
-      <c r="C14" s="29" t="n">
-        <v>1200</v>
-      </c>
-      <c r="D14" s="29" t="n">
-        <v>621</v>
-      </c>
-      <c r="E14" s="30" t="n">
-        <v>0.46</v>
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>Октябрь</t>
+        </is>
+      </c>
+      <c r="B14" s="25" t="n">
+        <v>1395</v>
+      </c>
+      <c r="C14" s="25" t="n">
+        <v>1311</v>
+      </c>
+      <c r="D14" s="25" t="n"/>
+      <c r="E14" s="25" t="n">
+        <v>1183</v>
+      </c>
+      <c r="F14" s="25" t="n">
+        <v>788</v>
+      </c>
+      <c r="G14" s="25" t="n">
+        <v>1477</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="28" t="inlineStr">
-        <is>
-          <t>Июль</t>
-        </is>
-      </c>
-      <c r="B15" s="29" t="n">
-        <v>1409</v>
-      </c>
-      <c r="C15" s="29" t="n">
-        <v>1213</v>
-      </c>
-      <c r="D15" s="29" t="n">
-        <v>650</v>
-      </c>
-      <c r="E15" s="30" t="n">
-        <v>0.46</v>
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>Ноябрь</t>
+        </is>
+      </c>
+      <c r="B15" s="25" t="n">
+        <v>1367</v>
+      </c>
+      <c r="C15" s="25" t="n">
+        <v>1111</v>
+      </c>
+      <c r="D15" s="25" t="n"/>
+      <c r="E15" s="25" t="n">
+        <v>1095</v>
+      </c>
+      <c r="F15" s="25" t="n">
+        <v>588</v>
+      </c>
+      <c r="G15" s="25" t="n">
+        <v>1448</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="28" t="inlineStr">
-        <is>
-          <t>Август</t>
-        </is>
-      </c>
-      <c r="B16" s="29" t="n">
-        <v>1328</v>
-      </c>
-      <c r="C16" s="29" t="n">
-        <v>1220</v>
-      </c>
-      <c r="D16" s="29" t="n">
-        <v>613</v>
-      </c>
-      <c r="E16" s="30" t="n">
-        <v>0.46</v>
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>Декабрь</t>
+        </is>
+      </c>
+      <c r="B16" s="25" t="n">
+        <v>1622</v>
+      </c>
+      <c r="C16" s="25" t="n">
+        <v>2085</v>
+      </c>
+      <c r="D16" s="25" t="n"/>
+      <c r="E16" s="25" t="n">
+        <v>1574</v>
+      </c>
+      <c r="F16" s="25" t="n">
+        <v>1305</v>
+      </c>
+      <c r="G16" s="25" t="n">
+        <v>1719</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="28" t="inlineStr">
-        <is>
-          <t>Сентябрь</t>
-        </is>
-      </c>
-      <c r="B17" s="29" t="n">
-        <v>1358</v>
-      </c>
-      <c r="C17" s="29" t="n">
-        <v>1228</v>
-      </c>
-      <c r="D17" s="29" t="n">
-        <v>627</v>
-      </c>
-      <c r="E17" s="30" t="n">
-        <v>0.46</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="28" t="inlineStr">
-        <is>
-          <t>Октябрь</t>
-        </is>
-      </c>
-      <c r="B18" s="29" t="n">
-        <v>1625</v>
-      </c>
-      <c r="C18" s="29" t="n">
-        <v>1422</v>
-      </c>
-      <c r="D18" s="29" t="n">
-        <v>750</v>
-      </c>
-      <c r="E18" s="30" t="n">
-        <v>0.46</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="28" t="inlineStr">
-        <is>
-          <t>Ноябрь</t>
-        </is>
-      </c>
-      <c r="B19" s="29" t="n">
-        <v>1517</v>
-      </c>
-      <c r="C19" s="29" t="n">
-        <v>1368</v>
-      </c>
-      <c r="D19" s="29" t="n">
-        <v>700</v>
-      </c>
-      <c r="E19" s="30" t="n">
-        <v>0.46</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="28" t="inlineStr">
-        <is>
-          <t>Декабрь</t>
-        </is>
-      </c>
-      <c r="B20" s="29" t="n">
-        <v>1544</v>
-      </c>
-      <c r="C20" s="29" t="n">
-        <v>1395</v>
-      </c>
-      <c r="D20" s="29" t="n">
-        <v>713</v>
-      </c>
-      <c r="E20" s="30" t="n">
-        <v>0.46</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="31" t="inlineStr">
-        <is>
-          <t>Итого 2026</t>
-        </is>
-      </c>
-      <c r="B21" s="32" t="n">
-        <v>17196</v>
-      </c>
-      <c r="C21" s="32" t="n">
-        <v>14992</v>
-      </c>
-      <c r="D21" s="32" t="n">
-        <v>7938</v>
-      </c>
-      <c r="E21" s="33" t="n">
-        <v>0.46</v>
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>ИТОГО год</t>
+        </is>
+      </c>
+      <c r="B17" s="27" t="n">
+        <v>16033</v>
+      </c>
+      <c r="C17" s="27" t="n"/>
+      <c r="D17" s="27" t="n">
+        <v>6928</v>
+      </c>
+      <c r="E17" s="27" t="n">
+        <v>15396</v>
+      </c>
+      <c r="F17" s="27" t="n">
+        <v>12955</v>
+      </c>
+      <c r="G17" s="27" t="n">
+        <v>16985</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Прогноз 2026 — Маркет и ОФД (с лидами).xlsx
+++ b/Прогноз 2026 — Маркет и ОФД (с лидами).xlsx
@@ -11,13 +11,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Маркет (выручка)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Маркет (оплаты)" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Маркет (лиды)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ОФД (выручка)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ОФД (оплаты)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ОФД (лиды)" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сравнение методов" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Реклама — эффективность" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Методология" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Данные (вход)" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Маркет (горячие)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ОФД (выручка)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ОФД (оплаты)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ОФД (лиды)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ОФД (горячие)" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сравнение методов" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Реклама — эффективность" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Методология" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Данные (вход)" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30,7 +32,7 @@
     <numFmt numFmtId="164" formatCode="#,##0 ₽"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -88,6 +90,12 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Montserrat"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -133,7 +141,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -172,6 +180,9 @@
     <xf numFmtId="3" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="10" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -250,7 +261,6 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="2"/>
   <chart>
     <title>
       <tx>
@@ -441,7 +451,6 @@
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="2"/>
   <chart>
     <title>
       <tx>
@@ -632,7 +641,6 @@
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="2"/>
   <chart>
     <title>
       <tx>
@@ -823,7 +831,146 @@
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Маркет: горячие заявки — 2025 факт vs 2026 прогноз</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Маркет (горячие)'!D4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
+              <a:solidFill>
+                <a:srgbClr val="C2C8D0"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="5"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="C2C8D0"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Маркет (горячие)'!$A$5:$A$16</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Маркет (горячие)'!$D$5:$D$16</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Маркет (горячие)'!E4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
+              <a:solidFill>
+                <a:srgbClr val="2291FF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="5"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="2291FF"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Маркет (горячие)'!$A$5:$A$16</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Маркет (горячие)'!$E$5:$E$16</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <smooth val="0"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
@@ -1012,9 +1159,8 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="2"/>
   <chart>
     <title>
       <tx>
@@ -1203,9 +1349,8 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="2"/>
   <chart>
     <title>
       <tx>
@@ -1394,6 +1539,146 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>ОФД: горячие заявки — 2025 факт vs 2026 прогноз</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'ОФД (горячие)'!D4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
+              <a:solidFill>
+                <a:srgbClr val="C2C8D0"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="5"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="C2C8D0"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'ОФД (горячие)'!$A$5:$A$16</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'ОФД (горячие)'!$D$5:$D$16</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'ОФД (горячие)'!E4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
+              <a:solidFill>
+                <a:srgbClr val="2291FF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="5"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="2291FF"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'ОФД (горячие)'!$A$5:$A$16</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'ОФД (горячие)'!$E$5:$E$16</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <smooth val="0"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -1530,6 +1815,60 @@
 </file>
 
 <file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="2951999"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="2951999"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -2250,6 +2589,765 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Прогноз года по методам (выручка), ₽</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Ансамбль (база) — взвешенное среднее: pacing 0.40 · YoY 0.25 · ETS 0.15 · регрессия 0.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Метод</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>ОФД</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Plan-pacing</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>107967248.3546386</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>46355202.65119191</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Сезонный YoY</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>97631341.61583415</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>40564908.19614005</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>ETS / Holt</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>102360063.267196</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>44668260.26461965</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Регрессия+сезон</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>95234846.80000003</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>39671501.93799989</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>АНСАМБЛЬ (база)</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="n">
+        <v>101995713.5958934</v>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>43317847.53680471</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Контекстная реклама: расход / оплаты / CPO / CPL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Источник: дашборды Контекст (распознано с экрана, суммы сверены с «Итого»). Выручка по целевым лидам — из data (15). Июнь 2026 — неполный.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Месяц</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Маркет расход</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Маркет опл.</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Маркет CPO</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Маркет CPL</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>ОФД расход</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>ОФД опл.</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>ОФД CPO</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>ОФД CPL</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>янв 2025</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>1426675</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>129698</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>16212</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>349519</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>8738</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>2608</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>фев 2025</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>1458662</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>85804</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>14301</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>417835</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>11938</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>4096</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>мар 2025</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>1291864</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>92276</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>14680</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>457771</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>22889</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>4976</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>апр 2025</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>1653242</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>53330</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>13018</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>586537</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>34502</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>8626</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>май 2025</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>1140537</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>47522</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>9666</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>524111</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>47646</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>10079</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>июн 2025</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>892872</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>34341</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>8504</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>426952</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>53369</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>9282</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>июл 2025</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>679389</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>33969</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>6596</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>356743</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>14864</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>4694</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>авг 2025</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>468224</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>29264</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>8361</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>367080</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>19320</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>4706</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>сен 2025</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>624524</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>31226</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>8217</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>405867</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>20293</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>4560</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>окт 2025</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>827573</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>45976</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>11034</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>460200</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>21914</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>5171</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>ноя 2025</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>751818</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>68347</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>11221</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>432649</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>18811</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>4973</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>дек 2025</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>637877</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>39867</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>9665</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>386677</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>12889</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>3906</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>янв 2026</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>566120</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>24614</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>7650</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>415847</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>12995</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>3465</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>фев 2026</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>562249</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>37483</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>9694</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>386770</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>13337</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>3484</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>мар 2026</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>704396</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>46960</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>10513</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>423647</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>16946</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>3560</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>апр 2026</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>449859</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>26462</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>5998</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>390294</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>18585</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>3199</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>май 2026</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>467277</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>23364</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>4537</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>262720</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>14596</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>4042</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>июн 2026</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>129019</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>129019</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>4608</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>52264</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>13066</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>1936</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2461,7 +3559,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3954,342 +5052,388 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ОФД — выручка 2026, помесячно</t>
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>Маркет — горячие заявки, помесячно</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Проекты Проект п453 · Подключение · Онлайн · факт по Май, далее прогноз (база) и коридор низ/верх</t>
+      <c r="A2" s="22" t="inlineStr">
+        <is>
+          <t>Воронка заявок: всего → горячие → горячие без поставки/счёта · 2025 факт, 2026 прогноз · YoY горячих -12%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>Месяц</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>План 2026</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Факт 2025</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Факт 2026</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Прогноз база</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Прогноз низ</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Прогноз верх</t>
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>Заявок 2025</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>Заявок 2026</t>
+        </is>
+      </c>
+      <c r="D4" s="28" t="inlineStr">
+        <is>
+          <t>Горячих 2025</t>
+        </is>
+      </c>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>Горячих 2026</t>
+        </is>
+      </c>
+      <c r="F4" s="28" t="inlineStr">
+        <is>
+          <t>Гор. без поставки 2025</t>
+        </is>
+      </c>
+      <c r="G4" s="28" t="inlineStr">
+        <is>
+          <t>Гор. без поставки 2026</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t>Январь</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
-        <v>2810129.792756177</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>4247510.21</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>4051268</v>
-      </c>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n"/>
+      <c r="B5" s="25" t="n">
+        <v>2489</v>
+      </c>
+      <c r="C5" s="25" t="n">
+        <v>1763</v>
+      </c>
+      <c r="D5" s="25" t="n">
+        <v>1591</v>
+      </c>
+      <c r="E5" s="25" t="n">
+        <v>1053</v>
+      </c>
+      <c r="F5" s="25" t="n">
+        <v>1195</v>
+      </c>
+      <c r="G5" s="25" t="n">
+        <v>785</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="24" t="inlineStr">
         <is>
           <t>Февраль</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
-        <v>3106809.006335288</v>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>4139667.24</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>4117291.34</v>
-      </c>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
+      <c r="B6" s="25" t="n">
+        <v>2266</v>
+      </c>
+      <c r="C6" s="25" t="n">
+        <v>1857</v>
+      </c>
+      <c r="D6" s="25" t="n">
+        <v>1363</v>
+      </c>
+      <c r="E6" s="25" t="n">
+        <v>1109</v>
+      </c>
+      <c r="F6" s="25" t="n">
+        <v>1037</v>
+      </c>
+      <c r="G6" s="25" t="n">
+        <v>827</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="24" t="inlineStr">
         <is>
           <t>Март</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
-        <v>3178600.318375708</v>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>4230686.78</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>4177257.07</v>
-      </c>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
+      <c r="B7" s="25" t="n">
+        <v>2235</v>
+      </c>
+      <c r="C7" s="25" t="n">
+        <v>2013</v>
+      </c>
+      <c r="D7" s="25" t="n">
+        <v>1387</v>
+      </c>
+      <c r="E7" s="25" t="n">
+        <v>1203</v>
+      </c>
+      <c r="F7" s="25" t="n">
+        <v>1058</v>
+      </c>
+      <c r="G7" s="25" t="n">
+        <v>897</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="24" t="inlineStr">
         <is>
           <t>Апрель</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n">
-        <v>3241746.667406957</v>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>5801236.93</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>3708388.14</v>
-      </c>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="6" t="n"/>
+      <c r="B8" s="25" t="n">
+        <v>2384</v>
+      </c>
+      <c r="C8" s="25" t="n">
+        <v>1951</v>
+      </c>
+      <c r="D8" s="25" t="n">
+        <v>1334</v>
+      </c>
+      <c r="E8" s="25" t="n">
+        <v>1166</v>
+      </c>
+      <c r="F8" s="25" t="n">
+        <v>1018</v>
+      </c>
+      <c r="G8" s="25" t="n">
+        <v>869</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="24" t="inlineStr">
         <is>
           <t>Май</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n">
-        <v>2968801.044866289</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>4003480.27</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>2843729.85</v>
-      </c>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="n"/>
+      <c r="B9" s="25" t="n">
+        <v>1842</v>
+      </c>
+      <c r="C9" s="25" t="n">
+        <v>1810</v>
+      </c>
+      <c r="D9" s="25" t="n">
+        <v>1061</v>
+      </c>
+      <c r="E9" s="25" t="n">
+        <v>1081</v>
+      </c>
+      <c r="F9" s="25" t="n">
+        <v>776</v>
+      </c>
+      <c r="G9" s="25" t="n">
+        <v>806</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="24" t="inlineStr">
         <is>
           <t>Июнь</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n">
-        <v>3042927.784869445</v>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>4119078.85</v>
-      </c>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n">
-        <v>3607218.915260342</v>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>3414149.443999988</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>3757005.320959318</v>
+      <c r="B10" s="25" t="n">
+        <v>2078</v>
+      </c>
+      <c r="C10" s="25" t="n">
+        <v>1629</v>
+      </c>
+      <c r="D10" s="25" t="n">
+        <v>1278</v>
+      </c>
+      <c r="E10" s="25" t="n">
+        <v>973</v>
+      </c>
+      <c r="F10" s="25" t="n">
+        <v>981</v>
+      </c>
+      <c r="G10" s="25" t="n">
+        <v>725</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="24" t="inlineStr">
         <is>
           <t>Июль</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n">
-        <v>3031387.357925069</v>
-      </c>
-      <c r="C11" s="6" t="n">
-        <v>3662365.2</v>
-      </c>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n">
-        <v>3413275.795122174</v>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>2957435.793999986</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>3742756.726020012</v>
+      <c r="B11" s="25" t="n">
+        <v>2038</v>
+      </c>
+      <c r="C11" s="25" t="n">
+        <v>1645</v>
+      </c>
+      <c r="D11" s="25" t="n">
+        <v>1218</v>
+      </c>
+      <c r="E11" s="25" t="n">
+        <v>983</v>
+      </c>
+      <c r="F11" s="25" t="n">
+        <v>882</v>
+      </c>
+      <c r="G11" s="25" t="n">
+        <v>733</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="24" t="inlineStr">
         <is>
           <t>Август</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n">
-        <v>2992991.751534346</v>
-      </c>
-      <c r="C12" s="6" t="n">
-        <v>3036270.56</v>
-      </c>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n">
-        <v>3136636.550911444</v>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>2331341.153999985</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>3695350.902513886</v>
+      <c r="B12" s="25" t="n">
+        <v>1790</v>
+      </c>
+      <c r="C12" s="25" t="n">
+        <v>1667</v>
+      </c>
+      <c r="D12" s="25" t="n">
+        <v>1084</v>
+      </c>
+      <c r="E12" s="25" t="n">
+        <v>996</v>
+      </c>
+      <c r="F12" s="25" t="n">
+        <v>774</v>
+      </c>
+      <c r="G12" s="25" t="n">
+        <v>742</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="24" t="inlineStr">
         <is>
           <t>Сентябрь</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n">
-        <v>2901984.613445907</v>
-      </c>
-      <c r="C13" s="6" t="n">
-        <v>3091534.05</v>
-      </c>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n">
-        <v>3113955.313009272</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>2386604.643999983</v>
-      </c>
-      <c r="G13" s="6" t="n">
-        <v>3680312.910176613</v>
+      <c r="B13" s="25" t="n">
+        <v>1821</v>
+      </c>
+      <c r="C13" s="25" t="n">
+        <v>1620</v>
+      </c>
+      <c r="D13" s="25" t="n">
+        <v>1109</v>
+      </c>
+      <c r="E13" s="25" t="n">
+        <v>968</v>
+      </c>
+      <c r="F13" s="25" t="n">
+        <v>810</v>
+      </c>
+      <c r="G13" s="25" t="n">
+        <v>721</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="24" t="inlineStr">
         <is>
           <t>Октябрь</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n">
-        <v>3277976.709883101</v>
-      </c>
-      <c r="C14" s="6" t="n">
-        <v>3457517.25</v>
-      </c>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n">
-        <v>3449607.984927707</v>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>2752587.843999983</v>
-      </c>
-      <c r="G14" s="6" t="n">
-        <v>4047212.688466714</v>
+      <c r="B14" s="25" t="n">
+        <v>1964</v>
+      </c>
+      <c r="C14" s="25" t="n">
+        <v>1726</v>
+      </c>
+      <c r="D14" s="25" t="n">
+        <v>1165</v>
+      </c>
+      <c r="E14" s="25" t="n">
+        <v>1031</v>
+      </c>
+      <c r="F14" s="25" t="n">
+        <v>866</v>
+      </c>
+      <c r="G14" s="25" t="n">
+        <v>769</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="24" t="inlineStr">
         <is>
           <t>Ноябрь</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n">
-        <v>3197016.051724652</v>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>2915834.57</v>
-      </c>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n">
-        <v>3186874.829107625</v>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>2210905.163999981</v>
-      </c>
-      <c r="G15" s="6" t="n">
-        <v>3947253.161000401</v>
+      <c r="B15" s="25" t="n">
+        <v>1658</v>
+      </c>
+      <c r="C15" s="25" t="n">
+        <v>1841</v>
+      </c>
+      <c r="D15" s="25" t="n">
+        <v>951</v>
+      </c>
+      <c r="E15" s="25" t="n">
+        <v>1100</v>
+      </c>
+      <c r="F15" s="25" t="n">
+        <v>708</v>
+      </c>
+      <c r="G15" s="25" t="n">
+        <v>820</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="24" t="inlineStr">
         <is>
           <t>Декабрь</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n">
-        <v>3794301.338165053</v>
-      </c>
-      <c r="C16" s="6" t="n">
-        <v>5425472.9</v>
-      </c>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n">
-        <v>4512343.748466134</v>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>3674639.974324989</v>
-      </c>
-      <c r="G16" s="6" t="n">
-        <v>4720543.493999979</v>
+      <c r="B16" s="25" t="n">
+        <v>1523</v>
+      </c>
+      <c r="C16" s="25" t="n">
+        <v>1642</v>
+      </c>
+      <c r="D16" s="25" t="n">
+        <v>853</v>
+      </c>
+      <c r="E16" s="25" t="n">
+        <v>981</v>
+      </c>
+      <c r="F16" s="25" t="n">
+        <v>626</v>
+      </c>
+      <c r="G16" s="25" t="n">
+        <v>731</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="26" t="inlineStr">
         <is>
           <t>ИТОГО год</t>
         </is>
       </c>
-      <c r="B17" s="14" t="n">
-        <v>37544672.43728799</v>
-      </c>
-      <c r="C17" s="13" t="n"/>
-      <c r="D17" s="14" t="n">
-        <v>18897934.4</v>
-      </c>
-      <c r="E17" s="14" t="n">
-        <v>43317847.53680471</v>
-      </c>
-      <c r="F17" s="14" t="n">
-        <v>38625598.4183249</v>
-      </c>
-      <c r="G17" s="14" t="n">
-        <v>46488369.60313693</v>
+      <c r="B17" s="27" t="n">
+        <v>24088</v>
+      </c>
+      <c r="C17" s="27" t="n">
+        <v>21164</v>
+      </c>
+      <c r="D17" s="27" t="n">
+        <v>14394</v>
+      </c>
+      <c r="E17" s="27" t="n">
+        <v>12644</v>
+      </c>
+      <c r="F17" s="27" t="n">
+        <v>10731</v>
+      </c>
+      <c r="G17" s="27" t="n">
+        <v>9425</v>
       </c>
     </row>
   </sheetData>
@@ -4319,7 +5463,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ОФД — оплаты 2026, помесячно</t>
+          <t>ОФД — выручка 2026, помесячно</t>
         </is>
       </c>
     </row>
@@ -4373,18 +5517,18 @@
           <t>Январь</t>
         </is>
       </c>
-      <c r="B5" s="11" t="n">
-        <v>553.1295998444964</v>
-      </c>
-      <c r="C5" s="11" t="n">
-        <v>925</v>
-      </c>
-      <c r="D5" s="11" t="n">
-        <v>712</v>
-      </c>
-      <c r="E5" s="11" t="n"/>
-      <c r="F5" s="11" t="n"/>
-      <c r="G5" s="11" t="n"/>
+      <c r="B5" s="6" t="n">
+        <v>2810129.792756177</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>4247510.21</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>4051268</v>
+      </c>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -4392,18 +5536,18 @@
           <t>Февраль</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n">
-        <v>611.4680998825025</v>
-      </c>
-      <c r="C6" s="11" t="n">
-        <v>800</v>
-      </c>
-      <c r="D6" s="11" t="n">
-        <v>699</v>
-      </c>
-      <c r="E6" s="11" t="n"/>
-      <c r="F6" s="11" t="n"/>
-      <c r="G6" s="11" t="n"/>
+      <c r="B6" s="6" t="n">
+        <v>3106809.006335288</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>4139667.24</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>4117291.34</v>
+      </c>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -4411,18 +5555,18 @@
           <t>Март</t>
         </is>
       </c>
-      <c r="B7" s="11" t="n">
-        <v>621.6022998825026</v>
-      </c>
-      <c r="C7" s="11" t="n">
-        <v>785</v>
-      </c>
-      <c r="D7" s="11" t="n">
-        <v>711</v>
-      </c>
-      <c r="E7" s="11" t="n"/>
-      <c r="F7" s="11" t="n"/>
-      <c r="G7" s="11" t="n"/>
+      <c r="B7" s="6" t="n">
+        <v>3178600.318375708</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>4230686.78</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>4177257.07</v>
+      </c>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -4430,18 +5574,18 @@
           <t>Апрель</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n">
-        <v>637.577022890739</v>
-      </c>
-      <c r="C8" s="11" t="n">
-        <v>1013</v>
-      </c>
-      <c r="D8" s="11" t="n">
-        <v>576</v>
-      </c>
-      <c r="E8" s="11" t="n"/>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="11" t="n"/>
+      <c r="B8" s="6" t="n">
+        <v>3241746.667406957</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>5801236.93</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>3708388.14</v>
+      </c>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -4449,18 +5593,18 @@
           <t>Май</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n">
-        <v>584.6209227040131</v>
-      </c>
-      <c r="C9" s="11" t="n">
-        <v>866</v>
-      </c>
-      <c r="D9" s="11" t="n">
-        <v>489</v>
-      </c>
-      <c r="E9" s="11" t="n"/>
-      <c r="F9" s="11" t="n"/>
-      <c r="G9" s="11" t="n"/>
+      <c r="B9" s="6" t="n">
+        <v>2968801.044866289</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>4003480.27</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>2843729.85</v>
+      </c>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -4468,21 +5612,21 @@
           <t>Июнь</t>
         </is>
       </c>
-      <c r="B10" s="11" t="n">
-        <v>597.8854260369515</v>
-      </c>
-      <c r="C10" s="11" t="n">
-        <v>726</v>
-      </c>
-      <c r="D10" s="11" t="n"/>
-      <c r="E10" s="11" t="n">
-        <v>574.3371580430527</v>
-      </c>
-      <c r="F10" s="11" t="n">
-        <v>485.5999999999999</v>
-      </c>
-      <c r="G10" s="11" t="n">
-        <v>633.3805857756607</v>
+      <c r="B10" s="6" t="n">
+        <v>3042927.784869445</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>4119078.85</v>
+      </c>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n">
+        <v>3607218.915260342</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>3414149.443999988</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>3757005.320959318</v>
       </c>
     </row>
     <row r="11">
@@ -4491,21 +5635,21 @@
           <t>Июль</t>
         </is>
       </c>
-      <c r="B11" s="11" t="n">
-        <v>594.5740260369514</v>
-      </c>
-      <c r="C11" s="11" t="n">
-        <v>627</v>
-      </c>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="11" t="n">
-        <v>534.6838385656411</v>
-      </c>
-      <c r="F11" s="11" t="n">
-        <v>386.6</v>
-      </c>
-      <c r="G11" s="11" t="n">
-        <v>629.8725951466871</v>
+      <c r="B11" s="6" t="n">
+        <v>3031387.357925069</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>3662365.2</v>
+      </c>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n">
+        <v>3413275.795122174</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>2957435.793999986</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>3742756.726020012</v>
       </c>
     </row>
     <row r="12">
@@ -4514,21 +5658,21 @@
           <t>Август</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n">
-        <v>584.9120258783644</v>
-      </c>
-      <c r="C12" s="11" t="n">
-        <v>586</v>
-      </c>
-      <c r="D12" s="11" t="n"/>
-      <c r="E12" s="11" t="n">
-        <v>514.5393659549742</v>
-      </c>
-      <c r="F12" s="11" t="n">
-        <v>345.6000000000001</v>
-      </c>
-      <c r="G12" s="11" t="n">
-        <v>619.6369830148199</v>
+      <c r="B12" s="6" t="n">
+        <v>2992991.751534346</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>3036270.56</v>
+      </c>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n">
+        <v>3136636.550911444</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>2331341.153999985</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>3695350.902513886</v>
       </c>
     </row>
     <row r="13">
@@ -4537,21 +5681,21 @@
           <t>Сентябрь</t>
         </is>
       </c>
-      <c r="B13" s="11" t="n">
-        <v>573.0697258783644</v>
-      </c>
-      <c r="C13" s="11" t="n">
-        <v>561</v>
-      </c>
-      <c r="D13" s="11" t="n"/>
-      <c r="E13" s="11" t="n">
-        <v>499.6359641188786</v>
-      </c>
-      <c r="F13" s="11" t="n">
-        <v>320.5999999999999</v>
-      </c>
-      <c r="G13" s="11" t="n">
-        <v>607.0916313733709</v>
+      <c r="B13" s="6" t="n">
+        <v>2901984.613445907</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>3091534.05</v>
+      </c>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n">
+        <v>3113955.313009272</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>2386604.643999983</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>3680312.910176613</v>
       </c>
     </row>
     <row r="14">
@@ -4560,21 +5704,21 @@
           <t>Октябрь</t>
         </is>
       </c>
-      <c r="B14" s="11" t="n">
-        <v>641.4724260369514</v>
-      </c>
-      <c r="C14" s="11" t="n">
-        <v>603</v>
-      </c>
-      <c r="D14" s="11" t="n"/>
-      <c r="E14" s="11" t="n">
-        <v>544.3503545490897</v>
-      </c>
-      <c r="F14" s="11" t="n">
-        <v>362.6</v>
-      </c>
-      <c r="G14" s="11" t="n">
-        <v>679.5552513385867</v>
+      <c r="B14" s="6" t="n">
+        <v>3277976.709883101</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>3457517.25</v>
+      </c>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n">
+        <v>3449607.984927707</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>2752587.843999983</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>4047212.688466714</v>
       </c>
     </row>
     <row r="15">
@@ -4583,21 +5727,21 @@
           <t>Ноябрь</t>
         </is>
       </c>
-      <c r="B15" s="11" t="n">
-        <v>628.7328258882317</v>
-      </c>
-      <c r="C15" s="11" t="n">
-        <v>511</v>
-      </c>
-      <c r="D15" s="11" t="n"/>
-      <c r="E15" s="11" t="n">
-        <v>503.5992871742177</v>
-      </c>
-      <c r="F15" s="11" t="n">
-        <v>270.6</v>
-      </c>
-      <c r="G15" s="11" t="n">
-        <v>666.0593287866208</v>
+      <c r="B15" s="6" t="n">
+        <v>3197016.051724652</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>2915834.57</v>
+      </c>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n">
+        <v>3186874.829107625</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>2210905.163999981</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>3947253.161000401</v>
       </c>
     </row>
     <row r="16">
@@ -4606,21 +5750,21 @@
           <t>Декабрь</t>
         </is>
       </c>
-      <c r="B16" s="11" t="n">
-        <v>746.2209264145296</v>
-      </c>
-      <c r="C16" s="11" t="n">
-        <v>959</v>
-      </c>
-      <c r="D16" s="11" t="n"/>
-      <c r="E16" s="11" t="n">
-        <v>724.0971884403589</v>
-      </c>
-      <c r="F16" s="11" t="n">
-        <v>600.51800642271</v>
-      </c>
-      <c r="G16" s="11" t="n">
-        <v>790.5224427753153</v>
+      <c r="B16" s="6" t="n">
+        <v>3794301.338165053</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>5425472.9</v>
+      </c>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n">
+        <v>4512343.748466134</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>3674639.974324989</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>4720543.493999979</v>
       </c>
     </row>
     <row r="17">
@@ -4629,21 +5773,21 @@
           <t>ИТОГО год</t>
         </is>
       </c>
-      <c r="B17" s="15" t="n">
-        <v>7375.265327374596</v>
+      <c r="B17" s="14" t="n">
+        <v>37544672.43728799</v>
       </c>
       <c r="C17" s="13" t="n"/>
-      <c r="D17" s="15" t="n">
-        <v>3187</v>
-      </c>
-      <c r="E17" s="15" t="n">
-        <v>7082.243156846213</v>
-      </c>
-      <c r="F17" s="15" t="n">
-        <v>5959.11800642271</v>
-      </c>
-      <c r="G17" s="15" t="n">
-        <v>7813.118818211061</v>
+      <c r="D17" s="14" t="n">
+        <v>18897934.4</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>43317847.53680471</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>38625598.4183249</v>
+      </c>
+      <c r="G17" s="14" t="n">
+        <v>46488369.60313693</v>
       </c>
     </row>
   </sheetData>
@@ -4653,6 +5797,360 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ОФД — оплаты 2026, помесячно</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Проекты Проект п453 · Подключение · Онлайн · факт по Май, далее прогноз (база) и коридор низ/верх</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Месяц</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>План 2026</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Факт 2025</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Факт 2026</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Прогноз база</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Прогноз низ</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Прогноз верх</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Январь</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="n">
+        <v>553.1295998444964</v>
+      </c>
+      <c r="C5" s="11" t="n">
+        <v>925</v>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>712</v>
+      </c>
+      <c r="E5" s="11" t="n"/>
+      <c r="F5" s="11" t="n"/>
+      <c r="G5" s="11" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Февраль</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n">
+        <v>611.4680998825025</v>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>699</v>
+      </c>
+      <c r="E6" s="11" t="n"/>
+      <c r="F6" s="11" t="n"/>
+      <c r="G6" s="11" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Март</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="n">
+        <v>621.6022998825026</v>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>785</v>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>711</v>
+      </c>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="11" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Апрель</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="n">
+        <v>637.577022890739</v>
+      </c>
+      <c r="C8" s="11" t="n">
+        <v>1013</v>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>576</v>
+      </c>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="11" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Май</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="n">
+        <v>584.6209227040131</v>
+      </c>
+      <c r="C9" s="11" t="n">
+        <v>866</v>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>489</v>
+      </c>
+      <c r="E9" s="11" t="n"/>
+      <c r="F9" s="11" t="n"/>
+      <c r="G9" s="11" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Июнь</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="n">
+        <v>597.8854260369515</v>
+      </c>
+      <c r="C10" s="11" t="n">
+        <v>726</v>
+      </c>
+      <c r="D10" s="11" t="n"/>
+      <c r="E10" s="11" t="n">
+        <v>574.3371580430527</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>485.5999999999999</v>
+      </c>
+      <c r="G10" s="11" t="n">
+        <v>633.3805857756607</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Июль</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="n">
+        <v>594.5740260369514</v>
+      </c>
+      <c r="C11" s="11" t="n">
+        <v>627</v>
+      </c>
+      <c r="D11" s="11" t="n"/>
+      <c r="E11" s="11" t="n">
+        <v>534.6838385656411</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>386.6</v>
+      </c>
+      <c r="G11" s="11" t="n">
+        <v>629.8725951466871</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Август</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="n">
+        <v>584.9120258783644</v>
+      </c>
+      <c r="C12" s="11" t="n">
+        <v>586</v>
+      </c>
+      <c r="D12" s="11" t="n"/>
+      <c r="E12" s="11" t="n">
+        <v>514.5393659549742</v>
+      </c>
+      <c r="F12" s="11" t="n">
+        <v>345.6000000000001</v>
+      </c>
+      <c r="G12" s="11" t="n">
+        <v>619.6369830148199</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Сентябрь</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="n">
+        <v>573.0697258783644</v>
+      </c>
+      <c r="C13" s="11" t="n">
+        <v>561</v>
+      </c>
+      <c r="D13" s="11" t="n"/>
+      <c r="E13" s="11" t="n">
+        <v>499.6359641188786</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>320.5999999999999</v>
+      </c>
+      <c r="G13" s="11" t="n">
+        <v>607.0916313733709</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Октябрь</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="n">
+        <v>641.4724260369514</v>
+      </c>
+      <c r="C14" s="11" t="n">
+        <v>603</v>
+      </c>
+      <c r="D14" s="11" t="n"/>
+      <c r="E14" s="11" t="n">
+        <v>544.3503545490897</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>362.6</v>
+      </c>
+      <c r="G14" s="11" t="n">
+        <v>679.5552513385867</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Ноябрь</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="n">
+        <v>628.7328258882317</v>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>511</v>
+      </c>
+      <c r="D15" s="11" t="n"/>
+      <c r="E15" s="11" t="n">
+        <v>503.5992871742177</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>270.6</v>
+      </c>
+      <c r="G15" s="11" t="n">
+        <v>666.0593287866208</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Декабрь</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n">
+        <v>746.2209264145296</v>
+      </c>
+      <c r="C16" s="11" t="n">
+        <v>959</v>
+      </c>
+      <c r="D16" s="11" t="n"/>
+      <c r="E16" s="11" t="n">
+        <v>724.0971884403589</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>600.51800642271</v>
+      </c>
+      <c r="G16" s="11" t="n">
+        <v>790.5224427753153</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>ИТОГО год</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="n">
+        <v>7375.265327374596</v>
+      </c>
+      <c r="C17" s="13" t="n"/>
+      <c r="D17" s="15" t="n">
+        <v>3187</v>
+      </c>
+      <c r="E17" s="15" t="n">
+        <v>7082.243156846213</v>
+      </c>
+      <c r="F17" s="15" t="n">
+        <v>5959.11800642271</v>
+      </c>
+      <c r="G17" s="15" t="n">
+        <v>7813.118818211061</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5006,761 +6504,402 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Прогноз года по методам (выручка), ₽</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Ансамбль (база) — взвешенное среднее: pacing 0.40 · YoY 0.25 · ETS 0.15 · регрессия 0.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Метод</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>ОФД</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Plan-pacing</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>107967248.3546386</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>46355202.65119191</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Сезонный YoY</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n">
-        <v>97631341.61583415</v>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>40564908.19614005</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>ETS / Holt</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n">
-        <v>102360063.267196</v>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>44668260.26461965</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Регрессия+сезон</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n">
-        <v>95234846.80000003</v>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>39671501.93799989</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="16" t="inlineStr">
-        <is>
-          <t>АНСАМБЛЬ (база)</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="n">
-        <v>101995713.5958934</v>
-      </c>
-      <c r="C9" s="14" t="n">
-        <v>43317847.53680471</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Контекстная реклама: расход / оплаты / CPO / CPL</t>
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>ОФД — горячие заявки, помесячно</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Источник: дашборды Контекст (распознано с экрана, суммы сверены с «Итого»). Выручка по целевым лидам — из data (15). Июнь 2026 — неполный.</t>
+      <c r="A2" s="22" t="inlineStr">
+        <is>
+          <t>Воронка заявок: всего → горячие → горячие без поставки/счёта · 2025 факт, 2026 прогноз · YoY горячих -11%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>Месяц</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Маркет расход</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Маркет опл.</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Маркет CPO</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Маркет CPL</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>ОФД расход</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>ОФД опл.</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>ОФД CPO</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>ОФД CPL</t>
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>Заявок 2025</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>Заявок 2026</t>
+        </is>
+      </c>
+      <c r="D4" s="28" t="inlineStr">
+        <is>
+          <t>Горячих 2025</t>
+        </is>
+      </c>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>Горячих 2026</t>
+        </is>
+      </c>
+      <c r="F4" s="28" t="inlineStr">
+        <is>
+          <t>Гор. без поставки 2025</t>
+        </is>
+      </c>
+      <c r="G4" s="28" t="inlineStr">
+        <is>
+          <t>Гор. без поставки 2026</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>янв 2025</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>1426675</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>129698</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>16212</v>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>349519</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>8738</v>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>2608</v>
+      <c r="A5" s="24" t="inlineStr">
+        <is>
+          <t>Январь</t>
+        </is>
+      </c>
+      <c r="B5" s="25" t="n">
+        <v>1133</v>
+      </c>
+      <c r="C5" s="25" t="n">
+        <v>1105</v>
+      </c>
+      <c r="D5" s="25" t="n">
+        <v>508</v>
+      </c>
+      <c r="E5" s="25" t="n">
+        <v>471</v>
+      </c>
+      <c r="F5" s="25" t="n">
+        <v>267</v>
+      </c>
+      <c r="G5" s="25" t="n">
+        <v>216</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>фев 2025</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n">
-        <v>1458662</v>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>85804</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>14301</v>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>417835</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="H6" s="6" t="n">
-        <v>11938</v>
-      </c>
-      <c r="I6" s="6" t="n">
-        <v>4096</v>
+      <c r="A6" s="24" t="inlineStr">
+        <is>
+          <t>Февраль</t>
+        </is>
+      </c>
+      <c r="B6" s="25" t="n">
+        <v>1340</v>
+      </c>
+      <c r="C6" s="25" t="n">
+        <v>1199</v>
+      </c>
+      <c r="D6" s="25" t="n">
+        <v>580</v>
+      </c>
+      <c r="E6" s="25" t="n">
+        <v>511</v>
+      </c>
+      <c r="F6" s="25" t="n">
+        <v>266</v>
+      </c>
+      <c r="G6" s="25" t="n">
+        <v>234</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>мар 2025</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n">
-        <v>1291864</v>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>92276</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>14680</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>457771</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>22889</v>
-      </c>
-      <c r="I7" s="6" t="n">
-        <v>4976</v>
+      <c r="A7" s="24" t="inlineStr">
+        <is>
+          <t>Март</t>
+        </is>
+      </c>
+      <c r="B7" s="25" t="n">
+        <v>1407</v>
+      </c>
+      <c r="C7" s="25" t="n">
+        <v>1217</v>
+      </c>
+      <c r="D7" s="25" t="n">
+        <v>573</v>
+      </c>
+      <c r="E7" s="25" t="n">
+        <v>519</v>
+      </c>
+      <c r="F7" s="25" t="n">
+        <v>295</v>
+      </c>
+      <c r="G7" s="25" t="n">
+        <v>238</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>апр 2025</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n">
-        <v>1653242</v>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>53330</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>13018</v>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>586537</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="H8" s="6" t="n">
-        <v>34502</v>
-      </c>
-      <c r="I8" s="6" t="n">
-        <v>8626</v>
+      <c r="A8" s="24" t="inlineStr">
+        <is>
+          <t>Апрель</t>
+        </is>
+      </c>
+      <c r="B8" s="25" t="n">
+        <v>1388</v>
+      </c>
+      <c r="C8" s="25" t="n">
+        <v>1161</v>
+      </c>
+      <c r="D8" s="25" t="n">
+        <v>601</v>
+      </c>
+      <c r="E8" s="25" t="n">
+        <v>495</v>
+      </c>
+      <c r="F8" s="25" t="n">
+        <v>288</v>
+      </c>
+      <c r="G8" s="25" t="n">
+        <v>227</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>май 2025</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>1140537</v>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>47522</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>9666</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>524111</v>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>47646</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>10079</v>
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>Май</t>
+        </is>
+      </c>
+      <c r="B9" s="25" t="n">
+        <v>1349</v>
+      </c>
+      <c r="C9" s="25" t="n">
+        <v>1210</v>
+      </c>
+      <c r="D9" s="25" t="n">
+        <v>598</v>
+      </c>
+      <c r="E9" s="25" t="n">
+        <v>516</v>
+      </c>
+      <c r="F9" s="25" t="n">
+        <v>247</v>
+      </c>
+      <c r="G9" s="25" t="n">
+        <v>236</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>июн 2025</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n">
-        <v>892872</v>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>34341</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>8504</v>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>426952</v>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>53369</v>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>9282</v>
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>Июнь</t>
+        </is>
+      </c>
+      <c r="B10" s="25" t="n">
+        <v>1612</v>
+      </c>
+      <c r="C10" s="25" t="n">
+        <v>1121</v>
+      </c>
+      <c r="D10" s="25" t="n">
+        <v>740</v>
+      </c>
+      <c r="E10" s="25" t="n">
+        <v>478</v>
+      </c>
+      <c r="F10" s="25" t="n">
+        <v>319</v>
+      </c>
+      <c r="G10" s="25" t="n">
+        <v>219</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>июл 2025</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n">
-        <v>679389</v>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>33969</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>6596</v>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>356743</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>14864</v>
-      </c>
-      <c r="I11" s="6" t="n">
-        <v>4694</v>
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>Июль</t>
+        </is>
+      </c>
+      <c r="B11" s="25" t="n">
+        <v>1612</v>
+      </c>
+      <c r="C11" s="25" t="n">
+        <v>1174</v>
+      </c>
+      <c r="D11" s="25" t="n">
+        <v>739</v>
+      </c>
+      <c r="E11" s="25" t="n">
+        <v>500</v>
+      </c>
+      <c r="F11" s="25" t="n">
+        <v>295</v>
+      </c>
+      <c r="G11" s="25" t="n">
+        <v>229</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>авг 2025</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n">
-        <v>468224</v>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="D12" s="6" t="n">
-        <v>29264</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>8361</v>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>367080</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="H12" s="6" t="n">
-        <v>19320</v>
-      </c>
-      <c r="I12" s="6" t="n">
-        <v>4706</v>
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>Август</t>
+        </is>
+      </c>
+      <c r="B12" s="25" t="n">
+        <v>1436</v>
+      </c>
+      <c r="C12" s="25" t="n">
+        <v>1107</v>
+      </c>
+      <c r="D12" s="25" t="n">
+        <v>599</v>
+      </c>
+      <c r="E12" s="25" t="n">
+        <v>472</v>
+      </c>
+      <c r="F12" s="25" t="n">
+        <v>286</v>
+      </c>
+      <c r="G12" s="25" t="n">
+        <v>216</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>сен 2025</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n">
-        <v>624524</v>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>31226</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>8217</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>405867</v>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="H13" s="6" t="n">
-        <v>20293</v>
-      </c>
-      <c r="I13" s="6" t="n">
-        <v>4560</v>
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>Сентябрь</t>
+        </is>
+      </c>
+      <c r="B13" s="25" t="n">
+        <v>1422</v>
+      </c>
+      <c r="C13" s="25" t="n">
+        <v>1132</v>
+      </c>
+      <c r="D13" s="25" t="n">
+        <v>598</v>
+      </c>
+      <c r="E13" s="25" t="n">
+        <v>482</v>
+      </c>
+      <c r="F13" s="25" t="n">
+        <v>282</v>
+      </c>
+      <c r="G13" s="25" t="n">
+        <v>221</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>окт 2025</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n">
-        <v>827573</v>
-      </c>
-      <c r="C14" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="D14" s="6" t="n">
-        <v>45976</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>11034</v>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>460200</v>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="H14" s="6" t="n">
-        <v>21914</v>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>5171</v>
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>Октябрь</t>
+        </is>
+      </c>
+      <c r="B14" s="25" t="n">
+        <v>1233</v>
+      </c>
+      <c r="C14" s="25" t="n">
+        <v>1354</v>
+      </c>
+      <c r="D14" s="25" t="n">
+        <v>499</v>
+      </c>
+      <c r="E14" s="25" t="n">
+        <v>577</v>
+      </c>
+      <c r="F14" s="25" t="n">
+        <v>204</v>
+      </c>
+      <c r="G14" s="25" t="n">
+        <v>264</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>ноя 2025</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n">
-        <v>751818</v>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>68347</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>11221</v>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>432649</v>
-      </c>
-      <c r="G15" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>18811</v>
-      </c>
-      <c r="I15" s="6" t="n">
-        <v>4973</v>
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>Ноябрь</t>
+        </is>
+      </c>
+      <c r="B15" s="25" t="n">
+        <v>1092</v>
+      </c>
+      <c r="C15" s="25" t="n">
+        <v>1264</v>
+      </c>
+      <c r="D15" s="25" t="n">
+        <v>403</v>
+      </c>
+      <c r="E15" s="25" t="n">
+        <v>539</v>
+      </c>
+      <c r="F15" s="25" t="n">
+        <v>184</v>
+      </c>
+      <c r="G15" s="25" t="n">
+        <v>247</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>дек 2025</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n">
-        <v>637877</v>
-      </c>
-      <c r="C16" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>39867</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>9665</v>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>386677</v>
-      </c>
-      <c r="G16" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="H16" s="6" t="n">
-        <v>12889</v>
-      </c>
-      <c r="I16" s="6" t="n">
-        <v>3906</v>
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>Декабрь</t>
+        </is>
+      </c>
+      <c r="B16" s="25" t="n">
+        <v>1003</v>
+      </c>
+      <c r="C16" s="25" t="n">
+        <v>1287</v>
+      </c>
+      <c r="D16" s="25" t="n">
+        <v>398</v>
+      </c>
+      <c r="E16" s="25" t="n">
+        <v>549</v>
+      </c>
+      <c r="F16" s="25" t="n">
+        <v>175</v>
+      </c>
+      <c r="G16" s="25" t="n">
+        <v>251</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>янв 2026</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n">
-        <v>566120</v>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>24614</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>7650</v>
-      </c>
-      <c r="F17" s="6" t="n">
-        <v>415847</v>
-      </c>
-      <c r="G17" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>12995</v>
-      </c>
-      <c r="I17" s="6" t="n">
-        <v>3465</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>фев 2026</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n">
-        <v>562249</v>
-      </c>
-      <c r="C18" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>37483</v>
-      </c>
-      <c r="E18" s="6" t="n">
-        <v>9694</v>
-      </c>
-      <c r="F18" s="6" t="n">
-        <v>386770</v>
-      </c>
-      <c r="G18" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="H18" s="6" t="n">
-        <v>13337</v>
-      </c>
-      <c r="I18" s="6" t="n">
-        <v>3484</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>мар 2026</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n">
-        <v>704396</v>
-      </c>
-      <c r="C19" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>46960</v>
-      </c>
-      <c r="E19" s="6" t="n">
-        <v>10513</v>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>423647</v>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>16946</v>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>3560</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>апр 2026</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n">
-        <v>449859</v>
-      </c>
-      <c r="C20" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="D20" s="6" t="n">
-        <v>26462</v>
-      </c>
-      <c r="E20" s="6" t="n">
-        <v>5998</v>
-      </c>
-      <c r="F20" s="6" t="n">
-        <v>390294</v>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="H20" s="6" t="n">
-        <v>18585</v>
-      </c>
-      <c r="I20" s="6" t="n">
-        <v>3199</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>май 2026</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n">
-        <v>467277</v>
-      </c>
-      <c r="C21" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="D21" s="6" t="n">
-        <v>23364</v>
-      </c>
-      <c r="E21" s="6" t="n">
-        <v>4537</v>
-      </c>
-      <c r="F21" s="6" t="n">
-        <v>262720</v>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>14596</v>
-      </c>
-      <c r="I21" s="6" t="n">
-        <v>4042</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>июн 2026</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="n">
-        <v>129019</v>
-      </c>
-      <c r="C22" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" s="6" t="n">
-        <v>129019</v>
-      </c>
-      <c r="E22" s="6" t="n">
-        <v>4608</v>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>52264</v>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="H22" s="6" t="n">
-        <v>13066</v>
-      </c>
-      <c r="I22" s="6" t="n">
-        <v>1936</v>
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>ИТОГО год</t>
+        </is>
+      </c>
+      <c r="B17" s="27" t="n">
+        <v>16027</v>
+      </c>
+      <c r="C17" s="27" t="n">
+        <v>14331</v>
+      </c>
+      <c r="D17" s="27" t="n">
+        <v>6836</v>
+      </c>
+      <c r="E17" s="27" t="n">
+        <v>6109</v>
+      </c>
+      <c r="F17" s="27" t="n">
+        <v>3108</v>
+      </c>
+      <c r="G17" s="27" t="n">
+        <v>2798</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Прогноз 2026 — Маркет и ОФД (с лидами).xlsx
+++ b/Прогноз 2026 — Маркет и ОФД (с лидами).xlsx
@@ -441,7 +441,7 @@
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="b"/>
+      <legendPos val="r"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -631,7 +631,7 @@
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="b"/>
+      <legendPos val="r"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -821,7 +821,7 @@
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="b"/>
+      <legendPos val="r"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -961,7 +961,7 @@
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="b"/>
+      <legendPos val="r"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -1151,7 +1151,7 @@
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="b"/>
+      <legendPos val="r"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -1341,7 +1341,7 @@
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="b"/>
+      <legendPos val="r"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -1531,7 +1531,7 @@
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="b"/>
+      <legendPos val="r"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -1671,7 +1671,7 @@
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="b"/>
+      <legendPos val="r"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -5053,11 +5053,11 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5070,7 +5070,7 @@
     <row r="2">
       <c r="A2" s="22" t="inlineStr">
         <is>
-          <t>Воронка заявок: всего → горячие → горячие без поставки/счёта · 2025 факт, 2026 прогноз · YoY горячих -12%</t>
+          <t>Воронка: всего → горячие → горячие без поставки/счёта · 2025 факт, 2026 — мой прогноз (ансамбль от факта 2025) · YoY горячих -17%</t>
         </is>
       </c>
     </row>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C4" s="28" t="inlineStr">
         <is>
-          <t>Заявок 2026</t>
+          <t>Заявок 2026 (прогноз)</t>
         </is>
       </c>
       <c r="D4" s="28" t="inlineStr">
@@ -5097,17 +5097,17 @@
       </c>
       <c r="E4" s="28" t="inlineStr">
         <is>
-          <t>Горячих 2026</t>
+          <t>Горячих 2026 (прогноз)</t>
         </is>
       </c>
       <c r="F4" s="28" t="inlineStr">
         <is>
-          <t>Гор. без поставки 2025</t>
+          <t>Без поставки 2025</t>
         </is>
       </c>
       <c r="G4" s="28" t="inlineStr">
         <is>
-          <t>Гор. без поставки 2026</t>
+          <t>Без поставки 2026 (прогноз)</t>
         </is>
       </c>
     </row>
@@ -5121,19 +5121,19 @@
         <v>2489</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>1763</v>
+        <v>2078</v>
       </c>
       <c r="D5" s="25" t="n">
         <v>1591</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>1053</v>
+        <v>1324</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>1195</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>785</v>
+        <v>987</v>
       </c>
     </row>
     <row r="6">
@@ -5146,19 +5146,19 @@
         <v>2266</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>1857</v>
+        <v>1892</v>
       </c>
       <c r="D6" s="25" t="n">
         <v>1363</v>
       </c>
       <c r="E6" s="25" t="n">
-        <v>1109</v>
+        <v>1135</v>
       </c>
       <c r="F6" s="25" t="n">
         <v>1037</v>
       </c>
       <c r="G6" s="25" t="n">
-        <v>827</v>
+        <v>857</v>
       </c>
     </row>
     <row r="7">
@@ -5171,19 +5171,19 @@
         <v>2235</v>
       </c>
       <c r="C7" s="25" t="n">
-        <v>2013</v>
+        <v>1866</v>
       </c>
       <c r="D7" s="25" t="n">
         <v>1387</v>
       </c>
       <c r="E7" s="25" t="n">
-        <v>1203</v>
+        <v>1154</v>
       </c>
       <c r="F7" s="25" t="n">
         <v>1058</v>
       </c>
       <c r="G7" s="25" t="n">
-        <v>897</v>
+        <v>874</v>
       </c>
     </row>
     <row r="8">
@@ -5196,19 +5196,19 @@
         <v>2384</v>
       </c>
       <c r="C8" s="25" t="n">
-        <v>1951</v>
+        <v>1991</v>
       </c>
       <c r="D8" s="25" t="n">
         <v>1334</v>
       </c>
       <c r="E8" s="25" t="n">
-        <v>1166</v>
+        <v>1110</v>
       </c>
       <c r="F8" s="25" t="n">
         <v>1018</v>
       </c>
       <c r="G8" s="25" t="n">
-        <v>869</v>
+        <v>841</v>
       </c>
     </row>
     <row r="9">
@@ -5221,19 +5221,19 @@
         <v>1842</v>
       </c>
       <c r="C9" s="25" t="n">
-        <v>1810</v>
+        <v>1538</v>
       </c>
       <c r="D9" s="25" t="n">
         <v>1061</v>
       </c>
       <c r="E9" s="25" t="n">
-        <v>1081</v>
+        <v>883</v>
       </c>
       <c r="F9" s="25" t="n">
         <v>776</v>
       </c>
       <c r="G9" s="25" t="n">
-        <v>806</v>
+        <v>641</v>
       </c>
     </row>
     <row r="10">
@@ -5246,19 +5246,19 @@
         <v>2078</v>
       </c>
       <c r="C10" s="25" t="n">
-        <v>1629</v>
+        <v>1735</v>
       </c>
       <c r="D10" s="25" t="n">
         <v>1278</v>
       </c>
       <c r="E10" s="25" t="n">
-        <v>973</v>
+        <v>1064</v>
       </c>
       <c r="F10" s="25" t="n">
         <v>981</v>
       </c>
       <c r="G10" s="25" t="n">
-        <v>725</v>
+        <v>810</v>
       </c>
     </row>
     <row r="11">
@@ -5271,19 +5271,19 @@
         <v>2038</v>
       </c>
       <c r="C11" s="25" t="n">
-        <v>1645</v>
+        <v>1702</v>
       </c>
       <c r="D11" s="25" t="n">
         <v>1218</v>
       </c>
       <c r="E11" s="25" t="n">
-        <v>983</v>
+        <v>1014</v>
       </c>
       <c r="F11" s="25" t="n">
         <v>882</v>
       </c>
       <c r="G11" s="25" t="n">
-        <v>733</v>
+        <v>729</v>
       </c>
     </row>
     <row r="12">
@@ -5296,19 +5296,19 @@
         <v>1790</v>
       </c>
       <c r="C12" s="25" t="n">
-        <v>1667</v>
+        <v>1495</v>
       </c>
       <c r="D12" s="25" t="n">
         <v>1084</v>
       </c>
       <c r="E12" s="25" t="n">
-        <v>996</v>
+        <v>902</v>
       </c>
       <c r="F12" s="25" t="n">
         <v>774</v>
       </c>
       <c r="G12" s="25" t="n">
-        <v>742</v>
+        <v>639</v>
       </c>
     </row>
     <row r="13">
@@ -5321,19 +5321,19 @@
         <v>1821</v>
       </c>
       <c r="C13" s="25" t="n">
-        <v>1620</v>
+        <v>1520</v>
       </c>
       <c r="D13" s="25" t="n">
         <v>1109</v>
       </c>
       <c r="E13" s="25" t="n">
-        <v>968</v>
+        <v>923</v>
       </c>
       <c r="F13" s="25" t="n">
         <v>810</v>
       </c>
       <c r="G13" s="25" t="n">
-        <v>721</v>
+        <v>669</v>
       </c>
     </row>
     <row r="14">
@@ -5346,19 +5346,19 @@
         <v>1964</v>
       </c>
       <c r="C14" s="25" t="n">
-        <v>1726</v>
+        <v>1640</v>
       </c>
       <c r="D14" s="25" t="n">
         <v>1165</v>
       </c>
       <c r="E14" s="25" t="n">
-        <v>1031</v>
+        <v>970</v>
       </c>
       <c r="F14" s="25" t="n">
         <v>866</v>
       </c>
       <c r="G14" s="25" t="n">
-        <v>769</v>
+        <v>715</v>
       </c>
     </row>
     <row r="15">
@@ -5371,19 +5371,19 @@
         <v>1658</v>
       </c>
       <c r="C15" s="25" t="n">
-        <v>1841</v>
+        <v>1384</v>
       </c>
       <c r="D15" s="25" t="n">
         <v>951</v>
       </c>
       <c r="E15" s="25" t="n">
-        <v>1100</v>
+        <v>792</v>
       </c>
       <c r="F15" s="25" t="n">
         <v>708</v>
       </c>
       <c r="G15" s="25" t="n">
-        <v>820</v>
+        <v>585</v>
       </c>
     </row>
     <row r="16">
@@ -5396,19 +5396,19 @@
         <v>1523</v>
       </c>
       <c r="C16" s="25" t="n">
-        <v>1642</v>
+        <v>1272</v>
       </c>
       <c r="D16" s="25" t="n">
         <v>853</v>
       </c>
       <c r="E16" s="25" t="n">
-        <v>981</v>
+        <v>710</v>
       </c>
       <c r="F16" s="25" t="n">
         <v>626</v>
       </c>
       <c r="G16" s="25" t="n">
-        <v>731</v>
+        <v>517</v>
       </c>
     </row>
     <row r="17">
@@ -5421,19 +5421,19 @@
         <v>24088</v>
       </c>
       <c r="C17" s="27" t="n">
-        <v>21164</v>
+        <v>20113</v>
       </c>
       <c r="D17" s="27" t="n">
         <v>14394</v>
       </c>
       <c r="E17" s="27" t="n">
-        <v>12644</v>
+        <v>11981</v>
       </c>
       <c r="F17" s="27" t="n">
         <v>10731</v>
       </c>
       <c r="G17" s="27" t="n">
-        <v>9425</v>
+        <v>8864</v>
       </c>
     </row>
   </sheetData>
@@ -6515,11 +6515,11 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6532,7 +6532,7 @@
     <row r="2">
       <c r="A2" s="22" t="inlineStr">
         <is>
-          <t>Воронка заявок: всего → горячие → горячие без поставки/счёта · 2025 факт, 2026 прогноз · YoY горячих -11%</t>
+          <t>Воронка: всего → горячие → горячие без поставки/счёта · 2025 факт, 2026 — мой прогноз (ансамбль от факта 2025) · YoY горячих -14%</t>
         </is>
       </c>
     </row>
@@ -6549,7 +6549,7 @@
       </c>
       <c r="C4" s="28" t="inlineStr">
         <is>
-          <t>Заявок 2026</t>
+          <t>Заявок 2026 (прогноз)</t>
         </is>
       </c>
       <c r="D4" s="28" t="inlineStr">
@@ -6559,17 +6559,17 @@
       </c>
       <c r="E4" s="28" t="inlineStr">
         <is>
-          <t>Горячих 2026</t>
+          <t>Горячих 2026 (прогноз)</t>
         </is>
       </c>
       <c r="F4" s="28" t="inlineStr">
         <is>
-          <t>Гор. без поставки 2025</t>
+          <t>Без поставки 2025</t>
         </is>
       </c>
       <c r="G4" s="28" t="inlineStr">
         <is>
-          <t>Гор. без поставки 2026</t>
+          <t>Без поставки 2026 (прогноз)</t>
         </is>
       </c>
     </row>
@@ -6583,19 +6583,19 @@
         <v>1133</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>1105</v>
+        <v>1025</v>
       </c>
       <c r="D5" s="25" t="n">
         <v>508</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>471</v>
+        <v>438</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>267</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6">
@@ -6608,19 +6608,19 @@
         <v>1340</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>1199</v>
+        <v>1212</v>
       </c>
       <c r="D6" s="25" t="n">
         <v>580</v>
       </c>
       <c r="E6" s="25" t="n">
-        <v>511</v>
+        <v>500</v>
       </c>
       <c r="F6" s="25" t="n">
         <v>266</v>
       </c>
       <c r="G6" s="25" t="n">
-        <v>234</v>
+        <v>217</v>
       </c>
     </row>
     <row r="7">
@@ -6633,19 +6633,19 @@
         <v>1407</v>
       </c>
       <c r="C7" s="25" t="n">
-        <v>1217</v>
+        <v>1273</v>
       </c>
       <c r="D7" s="25" t="n">
         <v>573</v>
       </c>
       <c r="E7" s="25" t="n">
-        <v>519</v>
+        <v>494</v>
       </c>
       <c r="F7" s="25" t="n">
         <v>295</v>
       </c>
       <c r="G7" s="25" t="n">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="8">
@@ -6658,19 +6658,19 @@
         <v>1388</v>
       </c>
       <c r="C8" s="25" t="n">
-        <v>1161</v>
+        <v>1256</v>
       </c>
       <c r="D8" s="25" t="n">
         <v>601</v>
       </c>
       <c r="E8" s="25" t="n">
-        <v>495</v>
+        <v>518</v>
       </c>
       <c r="F8" s="25" t="n">
         <v>288</v>
       </c>
       <c r="G8" s="25" t="n">
-        <v>227</v>
+        <v>234</v>
       </c>
     </row>
     <row r="9">
@@ -6683,7 +6683,7 @@
         <v>1349</v>
       </c>
       <c r="C9" s="25" t="n">
-        <v>1210</v>
+        <v>1221</v>
       </c>
       <c r="D9" s="25" t="n">
         <v>598</v>
@@ -6695,7 +6695,7 @@
         <v>247</v>
       </c>
       <c r="G9" s="25" t="n">
-        <v>236</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10">
@@ -6708,19 +6708,19 @@
         <v>1612</v>
       </c>
       <c r="C10" s="25" t="n">
-        <v>1121</v>
+        <v>1459</v>
       </c>
       <c r="D10" s="25" t="n">
         <v>740</v>
       </c>
       <c r="E10" s="25" t="n">
-        <v>478</v>
+        <v>638</v>
       </c>
       <c r="F10" s="25" t="n">
         <v>319</v>
       </c>
       <c r="G10" s="25" t="n">
-        <v>219</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11">
@@ -6733,19 +6733,19 @@
         <v>1612</v>
       </c>
       <c r="C11" s="25" t="n">
-        <v>1174</v>
+        <v>1459</v>
       </c>
       <c r="D11" s="25" t="n">
         <v>739</v>
       </c>
       <c r="E11" s="25" t="n">
-        <v>500</v>
+        <v>637</v>
       </c>
       <c r="F11" s="25" t="n">
         <v>295</v>
       </c>
       <c r="G11" s="25" t="n">
-        <v>229</v>
+        <v>240</v>
       </c>
     </row>
     <row r="12">
@@ -6758,19 +6758,19 @@
         <v>1436</v>
       </c>
       <c r="C12" s="25" t="n">
-        <v>1107</v>
+        <v>1299</v>
       </c>
       <c r="D12" s="25" t="n">
         <v>599</v>
       </c>
       <c r="E12" s="25" t="n">
-        <v>472</v>
+        <v>517</v>
       </c>
       <c r="F12" s="25" t="n">
         <v>286</v>
       </c>
       <c r="G12" s="25" t="n">
-        <v>216</v>
+        <v>233</v>
       </c>
     </row>
     <row r="13">
@@ -6783,19 +6783,19 @@
         <v>1422</v>
       </c>
       <c r="C13" s="25" t="n">
-        <v>1132</v>
+        <v>1287</v>
       </c>
       <c r="D13" s="25" t="n">
         <v>598</v>
       </c>
       <c r="E13" s="25" t="n">
-        <v>482</v>
+        <v>516</v>
       </c>
       <c r="F13" s="25" t="n">
         <v>282</v>
       </c>
       <c r="G13" s="25" t="n">
-        <v>221</v>
+        <v>230</v>
       </c>
     </row>
     <row r="14">
@@ -6808,19 +6808,19 @@
         <v>1233</v>
       </c>
       <c r="C14" s="25" t="n">
-        <v>1354</v>
+        <v>1116</v>
       </c>
       <c r="D14" s="25" t="n">
         <v>499</v>
       </c>
       <c r="E14" s="25" t="n">
-        <v>577</v>
+        <v>430</v>
       </c>
       <c r="F14" s="25" t="n">
         <v>204</v>
       </c>
       <c r="G14" s="25" t="n">
-        <v>264</v>
+        <v>166</v>
       </c>
     </row>
     <row r="15">
@@ -6833,19 +6833,19 @@
         <v>1092</v>
       </c>
       <c r="C15" s="25" t="n">
-        <v>1264</v>
+        <v>988</v>
       </c>
       <c r="D15" s="25" t="n">
         <v>403</v>
       </c>
       <c r="E15" s="25" t="n">
-        <v>539</v>
+        <v>348</v>
       </c>
       <c r="F15" s="25" t="n">
         <v>184</v>
       </c>
       <c r="G15" s="25" t="n">
-        <v>247</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16">
@@ -6858,19 +6858,19 @@
         <v>1003</v>
       </c>
       <c r="C16" s="25" t="n">
-        <v>1287</v>
+        <v>907</v>
       </c>
       <c r="D16" s="25" t="n">
         <v>398</v>
       </c>
       <c r="E16" s="25" t="n">
-        <v>549</v>
+        <v>343</v>
       </c>
       <c r="F16" s="25" t="n">
         <v>175</v>
       </c>
       <c r="G16" s="25" t="n">
-        <v>251</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17">
@@ -6883,19 +6883,19 @@
         <v>16027</v>
       </c>
       <c r="C17" s="27" t="n">
-        <v>14331</v>
+        <v>14502</v>
       </c>
       <c r="D17" s="27" t="n">
         <v>6836</v>
       </c>
       <c r="E17" s="27" t="n">
-        <v>6109</v>
+        <v>5895</v>
       </c>
       <c r="F17" s="27" t="n">
         <v>3108</v>
       </c>
       <c r="G17" s="27" t="n">
-        <v>2798</v>
+        <v>2530</v>
       </c>
     </row>
   </sheetData>

--- a/Прогноз 2026 — Маркет и ОФД (с лидами).xlsx
+++ b/Прогноз 2026 — Маркет и ОФД (с лидами).xlsx
@@ -2206,7 +2206,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Факт по Май включительно · модели: plan-pacing, сезонный YoY, ETS (statsmodels), регрессия (sklearn) · ансамбль и сценарии низ/база/верх</t>
+          <t>Факт по Май включительно · Маркет — база по plan-pacing (темп YTD 91%); ОФД — ансамбль · сценарии низ/база/верх</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>93076114.69332391</v>
+        <v>102374059</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>38625598.4183249</v>
@@ -2319,7 +2319,7 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>101995713.5958934</v>
+        <v>108326039</v>
       </c>
       <c r="C12" s="8" t="n">
         <v>43317847.53680471</v>
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>108426695.0560018</v>
+        <v>114278019</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>46488369.60313693</v>
@@ -2345,7 +2345,7 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.7818920119661682</v>
+        <v>0.86</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>1.028790395836917</v>
@@ -2358,7 +2358,7 @@
         </is>
       </c>
       <c r="B15" s="10" t="n">
-        <v>0.8568216881225098</v>
+        <v>0.91</v>
       </c>
       <c r="C15" s="10" t="n">
         <v>1.153768157364</v>
@@ -2371,7 +2371,7 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>0.9108455700747073</v>
+        <v>0.96</v>
       </c>
       <c r="C16" s="9" t="n">
         <v>1.238214814120109</v>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>недовыполнение</t>
+          <t>на грани плана</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="B26" s="11" t="n">
-        <v>4749.035887506989</v>
+        <v>5487</v>
       </c>
       <c r="C26" s="11" t="n">
         <v>5959.11800642271</v>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="B27" s="12" t="n">
-        <v>5370.971244904632</v>
+        <v>5798</v>
       </c>
       <c r="C27" s="12" t="n">
         <v>7082.243156846213</v>
@@ -2516,7 +2516,7 @@
         </is>
       </c>
       <c r="B28" s="11" t="n">
-        <v>5801.397388070602</v>
+        <v>6110</v>
       </c>
       <c r="C28" s="11" t="n">
         <v>7813.118818211061</v>
@@ -2529,7 +2529,7 @@
         </is>
       </c>
       <c r="B29" s="9" t="n">
-        <v>0.7421528188009048</v>
+        <v>0.857</v>
       </c>
       <c r="C29" s="9" t="n">
         <v>0.8079869322537312</v>
@@ -2542,7 +2542,7 @@
         </is>
       </c>
       <c r="B30" s="10" t="n">
-        <v>0.8393454047358389</v>
+        <v>0.906</v>
       </c>
       <c r="C30" s="10" t="n">
         <v>0.9602696096314284</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="B31" s="9" t="n">
-        <v>0.9066099996984844</v>
+        <v>0.955</v>
       </c>
       <c r="C31" s="9" t="n">
         <v>1.05936782900695</v>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>существенный недобор</t>
+          <t>недовыполнение</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -2611,6 +2611,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -2687,7 +2688,7 @@
         </is>
       </c>
       <c r="B9" s="14" t="n">
-        <v>101995713.5958934</v>
+        <v>108326039</v>
       </c>
       <c r="C9" s="14" t="n">
         <v>43317847.53680471</v>
@@ -4158,13 +4159,13 @@
       </c>
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="6" t="n">
-        <v>9101776.480453128</v>
+        <v>9413888.43</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>8534558.684505247</v>
+        <v>8536375.119999999</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>9360991.187623875</v>
+        <v>10291401.74</v>
       </c>
     </row>
     <row r="11">
@@ -4181,13 +4182,13 @@
       </c>
       <c r="D11" s="6" t="n"/>
       <c r="E11" s="6" t="n">
-        <v>8417917.967619848</v>
+        <v>9235376.42</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>7578916.400000003</v>
+        <v>8374503.06</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>9183482.244845971</v>
+        <v>10096249.77</v>
       </c>
     </row>
     <row r="12">
@@ -4204,13 +4205,13 @@
       </c>
       <c r="D12" s="6" t="n"/>
       <c r="E12" s="6" t="n">
-        <v>7203853.966861567</v>
+        <v>8219280.93</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>5578145.400000005</v>
+        <v>7453122.66</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>8344623.875908504</v>
+        <v>8985439.189999999</v>
       </c>
     </row>
     <row r="13">
@@ -4227,13 +4228,13 @@
       </c>
       <c r="D13" s="6" t="n"/>
       <c r="E13" s="6" t="n">
-        <v>7614401.594095069</v>
+        <v>8015691.33</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>6845849.400000002</v>
+        <v>7268510.62</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>8258569.730360099</v>
+        <v>8762872.039999999</v>
       </c>
     </row>
     <row r="14">
@@ -4250,13 +4251,13 @@
       </c>
       <c r="D14" s="6" t="n"/>
       <c r="E14" s="6" t="n">
-        <v>7845053.186182311</v>
+        <v>9074130.67</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>6397876.400000004</v>
+        <v>8228287.79</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>9023142.546251059</v>
+        <v>9919973.539999999</v>
       </c>
     </row>
     <row r="15">
@@ -4273,13 +4274,13 @@
       </c>
       <c r="D15" s="6" t="n"/>
       <c r="E15" s="6" t="n">
-        <v>7443083.243262713</v>
+        <v>8854830.869999999</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>5635354.400000005</v>
+        <v>8029429.97</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>8805075.005407915</v>
+        <v>9680231.76</v>
       </c>
     </row>
     <row r="16">
@@ -4296,13 +4297,13 @@
       </c>
       <c r="D16" s="6" t="n"/>
       <c r="E16" s="6" t="n">
-        <v>9895927.157418748</v>
+        <v>11039140.1</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>8031714.008818635</v>
+        <v>10010129.35</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>10977110.46560442</v>
+        <v>12068150.85</v>
       </c>
     </row>
     <row r="17">
@@ -4319,13 +4320,13 @@
         <v>44473700</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>101995713.5958934</v>
+        <v>108326038.75</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>93076114.69332391</v>
+        <v>102374058.57</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>108426695.0560018</v>
+        <v>114278018.89</v>
       </c>
     </row>
   </sheetData>
@@ -4512,13 +4513,13 @@
       </c>
       <c r="D10" s="11" t="n"/>
       <c r="E10" s="11" t="n">
-        <v>472.1624872282246</v>
+        <v>479.77</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>461.7158815494085</v>
+        <v>435.05</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>478.2101167315175</v>
+        <v>524.49</v>
       </c>
     </row>
     <row r="11">
@@ -4535,13 +4536,13 @@
       </c>
       <c r="D11" s="11" t="n"/>
       <c r="E11" s="11" t="n">
-        <v>440.9630121903972</v>
+        <v>512.61</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>356.0000000000001</v>
+        <v>464.82</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>504.7117281695287</v>
+        <v>560.39</v>
       </c>
     </row>
     <row r="12">
@@ -4558,13 +4559,13 @@
       </c>
       <c r="D12" s="11" t="n"/>
       <c r="E12" s="11" t="n">
-        <v>355.8579974503227</v>
+        <v>417.75</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>230.0000000000003</v>
+        <v>378.81</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>447.4082591923428</v>
+        <v>456.69</v>
       </c>
     </row>
     <row r="13">
@@ -4581,13 +4582,13 @@
       </c>
       <c r="D13" s="11" t="n"/>
       <c r="E13" s="11" t="n">
-        <v>383.6197751567994</v>
+        <v>435.08</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>288.9999999999999</v>
+        <v>394.52</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>441.14108741163</v>
+        <v>475.63</v>
       </c>
     </row>
     <row r="14">
@@ -4604,13 +4605,13 @@
       </c>
       <c r="D14" s="11" t="n"/>
       <c r="E14" s="11" t="n">
-        <v>416.6644812727669</v>
+        <v>509.87</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>301.0000000000001</v>
+        <v>462.34</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>502.0175374497625</v>
+        <v>557.4</v>
       </c>
     </row>
     <row r="15">
@@ -4627,13 +4628,13 @@
       </c>
       <c r="D15" s="11" t="n"/>
       <c r="E15" s="11" t="n">
-        <v>363.6620446519421</v>
+        <v>446.02</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>228.0000000000002</v>
+        <v>404.45</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>439.1530873218853</v>
+        <v>487.6</v>
       </c>
     </row>
     <row r="16">
@@ -4650,13 +4651,13 @@
       </c>
       <c r="D16" s="11" t="n"/>
       <c r="E16" s="11" t="n">
-        <v>480.0414469541792</v>
+        <v>539.0599999999999</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>425.3200059575791</v>
+        <v>488.81</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>530.7555717939349</v>
+        <v>589.3099999999999</v>
       </c>
     </row>
     <row r="17">
@@ -4673,13 +4674,13 @@
         <v>2458</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>5370.971244904632</v>
+        <v>5798.16</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>4749.035887506989</v>
+        <v>5486.8</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>5801.397388070602</v>
+        <v>6109.51</v>
       </c>
     </row>
   </sheetData>
@@ -4866,13 +4867,13 @@
       </c>
       <c r="D10" s="25" t="n"/>
       <c r="E10" s="25" t="n">
-        <v>1312</v>
+        <v>1332.59</v>
       </c>
       <c r="F10" s="25" t="n">
-        <v>1283</v>
+        <v>1208.38</v>
       </c>
       <c r="G10" s="25" t="n">
-        <v>1328</v>
+        <v>1456.81</v>
       </c>
     </row>
     <row r="11">
@@ -4889,13 +4890,13 @@
       </c>
       <c r="D11" s="25" t="n"/>
       <c r="E11" s="25" t="n">
-        <v>1225</v>
+        <v>1423.81</v>
       </c>
       <c r="F11" s="25" t="n">
-        <v>989</v>
+        <v>1291.09</v>
       </c>
       <c r="G11" s="25" t="n">
-        <v>1402</v>
+        <v>1556.53</v>
       </c>
     </row>
     <row r="12">
@@ -4912,13 +4913,13 @@
       </c>
       <c r="D12" s="25" t="n"/>
       <c r="E12" s="25" t="n">
-        <v>988</v>
+        <v>1160.21</v>
       </c>
       <c r="F12" s="25" t="n">
-        <v>639</v>
+        <v>1052.06</v>
       </c>
       <c r="G12" s="25" t="n">
-        <v>1243</v>
+        <v>1268.35</v>
       </c>
     </row>
     <row r="13">
@@ -4935,13 +4936,13 @@
       </c>
       <c r="D13" s="25" t="n"/>
       <c r="E13" s="25" t="n">
-        <v>1066</v>
+        <v>1208.55</v>
       </c>
       <c r="F13" s="25" t="n">
-        <v>803</v>
+        <v>1095.89</v>
       </c>
       <c r="G13" s="25" t="n">
-        <v>1225</v>
+        <v>1321.2</v>
       </c>
     </row>
     <row r="14">
@@ -4958,13 +4959,13 @@
       </c>
       <c r="D14" s="25" t="n"/>
       <c r="E14" s="25" t="n">
-        <v>1157</v>
+        <v>1416.51</v>
       </c>
       <c r="F14" s="25" t="n">
-        <v>836</v>
+        <v>1284.47</v>
       </c>
       <c r="G14" s="25" t="n">
-        <v>1394</v>
+        <v>1548.55</v>
       </c>
     </row>
     <row r="15">
@@ -4981,13 +4982,13 @@
       </c>
       <c r="D15" s="25" t="n"/>
       <c r="E15" s="25" t="n">
-        <v>1010</v>
+        <v>1238.65</v>
       </c>
       <c r="F15" s="25" t="n">
-        <v>633</v>
+        <v>1123.19</v>
       </c>
       <c r="G15" s="25" t="n">
-        <v>1220</v>
+        <v>1354.11</v>
       </c>
     </row>
     <row r="16">
@@ -5004,13 +5005,13 @@
       </c>
       <c r="D16" s="25" t="n"/>
       <c r="E16" s="25" t="n">
-        <v>1333</v>
+        <v>1497.69</v>
       </c>
       <c r="F16" s="25" t="n">
-        <v>1181</v>
+        <v>1358.08</v>
       </c>
       <c r="G16" s="25" t="n">
-        <v>1474</v>
+        <v>1637.29</v>
       </c>
     </row>
     <row r="17">
@@ -5027,13 +5028,13 @@
         <v>6828</v>
       </c>
       <c r="E17" s="27" t="n">
-        <v>14919</v>
+        <v>16106.01</v>
       </c>
       <c r="F17" s="27" t="n">
-        <v>13192</v>
+        <v>15241.16</v>
       </c>
       <c r="G17" s="27" t="n">
-        <v>16115</v>
+        <v>16970.84</v>
       </c>
     </row>
   </sheetData>
